--- a/sampled_contexts_for_human_annotation_v2.xlsx
+++ b/sampled_contexts_for_human_annotation_v2.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -456,10 +456,7 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,45 +527,30 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>section_bucket</t>
+          <t>manual_check_needed</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>relevance_bucket</t>
+          <t>human_alignment_check</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>q_bucket</t>
+          <t>human_primary_section</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>stratum</t>
+          <t>human_sentiment</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>human_primary_section</t>
+          <t>human_relevance</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>human_sentiment</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>human_relevance</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>human_alignment_check</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>annotation_note</t>
         </is>
@@ -582,17 +564,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>W3195579788-&gt;W3089176333</t>
+          <t>W2509511072-&gt;W1994174199</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Data pricing in machine learning pipelines</t>
+          <t>Understanding rollover data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Towards Query Pricing on Incomplete Data</t>
+          <t>Smart data pricing: To share or not to share?</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -602,73 +584,54 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miao X, Gao Y , Chen L, Peng H, Yin J, Li Q (2020) Towards query pricing on incomplete data. IEEE Trans Knowl Data Eng</t>
+          <t>Y . Jin and Z. Pang, “Smart data pricing: To share or not to share?,” Proc. IEEE Infocom Workshops on Smart Data Pricing , 2014.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Miao et al. [ 75] study the problem of pricing selection-projection-natural join queries over incomplete databases. An arbitrage-free pricing function is proposed based on the idea ofdata provenance, which describes the origins of a piece of data and its processing history [ 10, 107].
-... [another target-aligned mention] ...
-QueryMarket [ 59] tracks the purchased views of a customer and avoids charging those views when pricing future queries of the customer. Both[29]a n d[ 75] support history-aware pricing in the same vein as [ 59]. One drawback of these history-based approaches is that the seller must provide reliable storage to keep users’ queryhistory [ 111].
-... [another target-aligned mention] ...
-Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.</t>
+          <t>This heterogeneous data usage brings challenges todesigning mobile data plans, as the available monthly dataquotas may not ﬁt different users’ needs. Shared data plans [3]–[6] can help to even out the het- erogeneity in user demands by allowing multiple users anddevices to share one monthly quota of data usage. Taking thisone step further, users can even be allowed to trade leftoverdata with one another in a secondary data market [7]–[9].Thus, heavy users can reduce the likelihood of exceeding theirquotas by sharing or trading data caps with light users.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0.6091875</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -678,17 +641,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>W4210813858-&gt;W3084177365</t>
+          <t>W2509511072-&gt;W2010653253</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
+          <t>Understanding rollover data</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Data Pricing: From Economics to Data Science</t>
+          <t>A survey of smart data pricing</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -698,22 +661,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>J. Pei, ``A survey on data pricing: From economics to data science,'' IEEE Trans. Knowl. Data Eng., early access, Dec. 21, 2020, doi: 10.1109/TKDE.2020.3045927.</t>
+          <t>S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Surveys (CSUR) , vol. 46, no. 2, p. 15, 2013.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Recent studies and prac- tices have approached the commoditization of data in various ways, leading to the concepts of data pricing and data market. The associate editor coordinating the review of this manuscript and approving it for publication was Abdel-Hamid Soliman .Data pricing is to price data as asset and ensure that data can be sold or purchased as a commodity in business and economic activities [3]. The data market [4], [5] is where we trade data for revenue.</t>
+          <t>I. I NTRODUCTION Most Internet service providers (ISPs) today charge their users a ﬂat fee for a limited amount of mobile data that can be used each month, with steep overage fees for exceeding thismonthly quota [1]. Moreover, in most cases, leftover data atthe end of each month cannot be rolled over into subsequentmonths.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -723,44 +686,29 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0.02025</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -770,39 +718,37 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W2508874533-&gt;W2010653253</t>
+          <t>W4210813858-&gt;W2612128091</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Smart Media Pricing (SMP): Non-uniform packet pricing game for wireless multimedia communications</t>
+          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A survey of smart data pricing</t>
+          <t>QIRANA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>grouped</t>
+          <t>high_confidence</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[27]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Cisco, Cisco Visual Networking Index, “Global mobile data traf- ﬁc forecast update 2014–2019. white paper c11-520862,” Avail- able on http://www. cisco. com/c/en/us/solutions/collateral/service- provider/visual-networking-index-vni/white paper c11-520862. html . [2]S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “Smart data pricing (SDP): economic solutions to network congestion,” ACM SIGCOMM Recent Advances in Networking , pp. 221–274, 2013. [3]A. Mas-Colell, M. D. Whinston, J. R. Green et al. ,Microeconomic theory . Oxford university press New York, 1995, vol. 1. [4]S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Surveys (CSUR) , vol. 46, no. 2, p. 15, 2013. [5]P. Hande, M. Chiang, R. Calderbank, and J. Zhang, “Pricing under constraints in access networks: Revenue maximization and congestion management,” in Proceedings of IEEE INFOCOM , 2010, pp. 1–9. [6]M. Andrews, U. Ozen, M. Reiman, Q. Wang et al. , “Economic models of sponsored content in wireless networks with uncertain demand,” in Proceedings of IEEE INFOCOM , 2013, pp. 3213–3218. [7]C.-K. Chau, Q. Wang, and D.-M. Chiu, “On the viability of paris metro pricing for communication and service networks,” in Proceedings of IEEE INFOCOM , 2010, pp. 1–9. [8]S. Ha, S. Sen, C. Joe-Wong, Y. Im, and M. Chiang, “Tube: time- dependent pricing for mobile data,” ACM SIGCOMM Computer Com- munication Review , vol. 42, no. 4, pp. 247–258, 2012. [9]S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “Incentivizing time-shifting of data: a survey of time-dependent pricing for internet access,” IEEE Communications Magazine , vol. 50, no. 11, pp. 91–99, 2012.</t>
+          <t>S. Deep and P. Koutris, ``QIRANA: A framework for scalable query pricing,'' in Proc. ACM Int. Conf. Manage. Data , May 2017, pp. 699713.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. INTRODUCTION The Cisco Visual Network Index predicted that global mobile data trafﬁc will increase nearly tenfold between 2014 and 2019, and mobile video trafﬁc will account for 72% of the total mobile data trafﬁc by 2019 [1]. It will be enormous strain on already-overburdened mobile networks to meet this big multimedia data demand, which drives mobile network operators to innovate new pricing schemes.
-... [another target-aligned mention] ...
-The searching table can be updated with the dynamic estimated channel quality in spare time periods between transmitting video sequences. Then, the optimal power and price can be searched directly from the table when non-uniform SMP wasAlgorithm 1 : Non-Uniform Media Pricing Initialization: 1:Initialize the currency gain a, unit cost c, channel quality G, frequency bandwidth W, symbol rate Rs, noise power density N0, maximum iteration steps M, and distortion reduction Diand length Li; i2[1; N]. Iteration: 2:while i+ + 2[1; N]do 3: SetD=DiandL=Li; 4: Initialize Umax = 0; 5: Let =linspace (min; max; M); 6: while m= 1 :Mdo 7: Set= (m)and initialize P0= 0; 8: LetF(P) = Lexp ( </t>
+          <t>Researchers improved their studies and proposed a framework that allows the price of any query to be derived automatically [26]. QIRANA pricing sys- tem [27] allows exible pricing by allowing the data owners to choose from a variety of pricing functions, specify relation and attribute-level parameters to control the prices of queries. However, most queries considered by these marketplaces are too simplistic to support sophisticated data analytics and decision making.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -812,49 +758,34 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0.7200000000000001</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0.31205</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -864,91 +795,74 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2790400697</t>
+          <t>W4210813858-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>Query-Based Data Pricing</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>grouped</t>
+          <t>high_confidence</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>[26]</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Liang, F.; Yu, W.; An, D.; Yang, Q.; Fu, X.; Zhao, W. A Survey on Big Data Market: Pricing, Trading and Protection. IEEE Access 2018 ,6, 15132–15154. [CrossRef]</t>
+          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, ``Query- based data pricing,'' J. ACM, vol. 62, no. 5, pp. 144, Nov. 2015.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
-... [another target-aligned mention] ...
-Beyond empirical research, systematic literature reviews are also conducted to study data pricing opportunities and challenges in data marketplaces [ 138]. This approach is also employed to explore the different data pricing models in the data marketplace literature [47,139]. Other topics are auction-based pricing using the Bayesian mathematical model [140,141] , a pricing mechanism negotiation based on a negotiation game theory based in the energy domain [ 142], and a generic pricing mechanism based on a non-cooperative game the- ory in Mobile Crowdsensing [ 143].</t>
+          <t>Then data buyers submit queries to the platform, and the platform generates the objective function and corresponding constraints, forming an ILP problem to get the prices. Researchers improved their studies and proposed a framework that allows the price of any query to be derived automatically [26]. QIRANA pricing sys- tem [27] allows exible pricing by allowing the data owners to choose from a variety of pricing functions, specify relation and attribute-level parameters to control the prices of queries.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0.7200000000000001</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0.188538</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Discussion|mid|mid</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -958,97 +872,74 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>W3089176333-&gt;W2612128091</t>
+          <t>W4226305897-&gt;W2734426755</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Towards Query Pricing on Incomplete Data</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>QIRANA</t>
+          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>[16]</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>S. Deep and P. Koutris, “QIRANA: A framework for scalable query pricing,” in SIGMOD, pp. 699–713, 2017.</t>
+          <t>Zheng, Z.; Peng, Y.; Wu, F.; Tang, S.; Chen, G. An online pricing mechanism for mobile crowdsensing data markets. In Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing, Chennai, India, 10–14 July 2017; pp. 1–10.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>p3 2019-10-21 2019-11-01 t4u2? 2019-09-22 ?(c)Product(P) Pid Size Memory Price p14.7 64 $5988 p24.7 256 $7288 p35.5 64 $6888 p45.5 256 $8188 the literature [13], [14], [15], [16], [17], [18], [19]. However, these existing pricing approaches are notsuitable for pricing incomplete data, since they do not consider data complete- ness.
-... [another target-aligned mention] ...
-One can also compute other combined prices (e.g., the highest/average price) of lineage tuples for it. Moreover, the higher the tuple completeness, the higher the UCA price.The arbitrage-free property widely explored in relevant studies [13], [16], [19] is a typical and important property for price functions. This property is necessary for data pricing toavoid arbitrage .
-... [another target-aligned mention] ...
-Following existing studies [31], [7], [10], we simulate incomplete datasets via randomly discarding some values at a certain missing rate. In the experiments, following the related work [16], we use 40 queries over four datasets to conduct performance evaluation. All of the queries are described in Table 5, including 16 queries (w.r.t.
-... [another target-aligned mention] ...
-The seller sets the price of a speciﬁc set of base queries (also called view), and then, the algorithm has to derive the price of any other query that could be made to the database. This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51].
-... [another target-aligned mention] ...
-Our proposed pricing scheme iDBPricer belongs to the category. Q IRANA [16], [54], standing the viewpoint of the data buyer, employs the possible world semantic to price relational queries. In addition, there is a series of studies on pricing machine learning tasks [17], [18], [55], pricing-related problems in both advertising markets and labor markets [56], etc.</t>
+          <t>Another algorithm allows data price to be derived from the privacy losses [ 54]. Studies in query-based pricing mechanisms consider many cases such as query interfaces for mobile crowd-sensed data [ 55,56], cloud-based data mar- ketplaces with possibilities to share cloud resources [ 57], spatial data [ 58], aggregated data from multiple distributed system [ 59], and data acquired from Application Programming Interfaces (APIs) [ 60]. Moreover, Tang et al.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0.4428675000000001</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Result|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1058,22 +949,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>W3195579788-&gt;W2790400697</t>
+          <t>W4226305897-&gt;W2743929098</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Data pricing in machine learning pipelines</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>Data pricing strategy based on data quality</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>grouped</t>
+          <t>high_confidence</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1083,64 +974,49 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Liang F, Yu W, An D, Yang Q, Fu X, Zhao W (2018) A survey on big data market: pricing, trading and protection. IEEE Access 6:15132–15154</t>
+          <t>Yu, H.; Zhang, M. Data pricing strategy based on data quality. Comput. Ind. Eng. 2017 ,112, 1–10. [CrossRef]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Figure 1shows the connections of the four tasks. There are some previous surveys related to data pricing [ 35,63,120]. This article covers a substantially deeper and more focused scope than those.</t>
+          <t>[ 62] create efﬁcient query-based auctions by considering both the value data and the resource consumption of queries. Many other articles also propose data quality-based pricing models by considering a bi-level mathematical programming model [ 63], Fair Knapsack Pricing [ 64,65], or optimal distributing algorithm [ 66]. Other works on data quality-based pricing speciﬁcally focus on XML dataset properties [ 67,68].</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0.0215999999999999</t>
+          <t>0.1224999999999999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Introduction|low|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr"/>
-      <c r="V7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1150,89 +1026,78 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>W1994174199-&gt;W2950902070</t>
+          <t>W4226305897-&gt;W2765365501</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Smart data pricing: To share or not to share?</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>A Survey of Smart Data Pricing: Past Proposals, Current Plans, and Future Trends</t>
+          <t>Pricing of Data Products in Data Marketplaces</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>[181]</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Survey, vol. 46, no. 2, Nov. 2013.</t>
+          <t>Fricker, S.A.; Maksimov, Y.V . Pricing of data products in data marketplaces. In Proceedings of the International Conference of Software Business, Tallinn, Estonia, 11–12 June 2017; pp. 49–66.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In addition, Sen et al. [181] survey the major broad-band pricing proposals, including the realizations in various con- sumer data plans around the world. Murthy et al.</t>
+          <t>It focuses on technical discussions for data pricing. Computational pricing emphasizes algorithms as price determination mechanisms [ 47], such as machine learning-based algorithms to price training data or pre-trained models [48,49]. Advanced techniques are proposed, such as a smart pricing algorithm based on Stackelberg game theory.
+... [another target-aligned mention] ...
+[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
+... [another target-aligned mention] ...
+Beyond empirical research, systematic literature reviews are also conducted to study data pricing opportunities and challenges in data marketplaces [ 138]. This approach is also employed to explore the different data pricing models in the data marketplace literature [47,139]. Other topics are auction-based pricing using the Bayesian mathematical model [140,141] , a pricing mechanism negotiation based on a negotiation game theory based in the energy domain [ 142], and a generic pricing mechanism based on a non-cooperative game the- ory in Mobile Crowdsensing [ 143].</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0.02888</t>
+          <t>0.1889999999999999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Introduction|low|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1242,89 +1107,76 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>W3089176333-&gt;W2920282816</t>
+          <t>W4226305897-&gt;W2790400697</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Towards Query Pricing on Incomplete Data</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Pricing for Revenue Maximization in IoT Data Markets: An Information Design Perspective</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>[44]</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>W. Mao, Z. Zheng, and F. Wu, “Pricing for revenue maximization in iot data markets: An information design perspective,” in INFO- COM, pp. 1837–1845, 2019.</t>
+          <t>Liang, F.; Yu, W.; An, D.; Yang, Q.; Fu, X.; Zhao, W. A Survey on Big Data Market: Pricing, Trading and Protection. IEEE Access 2018 ,6, 15132–15154. [CrossRef]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51]. In contrast, another kind of pricing scheme considers the tuples of relations as the structural granularity of the pricing function [15], [26], [52], [53].</t>
+          <t>[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
+... [another target-aligned mention] ...
+Beyond empirical research, systematic literature reviews are also conducted to study data pricing opportunities and challenges in data marketplaces [ 138]. This approach is also employed to explore the different data pricing models in the data marketplace literature [47,139]. Other topics are auction-based pricing using the Bayesian mathematical model [140,141] , a pricing mechanism negotiation based on a negotiation game theory based in the energy domain [ 142], and a generic pricing mechanism based on a non-cooperative game the- ory in Mobile Crowdsensing [ 143].</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0.0067239999999999</t>
+          <t>0.1137499999999999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
-      <c r="V9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1334,7 +1186,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2018362551</t>
+          <t>W4226305897-&gt;W2920282816</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1344,81 +1196,66 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The challenges of personal data markets and privacy</t>
+          <t>Pricing for Revenue Maximization in IoT Data Markets: An Information Design Perspective</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Spiekermann, S.; Acquisti, A.; Böhme, R.; Hui, K.-L. The challenges of personal data markets and privacy. Electron. Mark. 2015 , 25, 161–167. [CrossRef]</t>
+          <t>Mao, W.; Zheng, Z.; Wu, F. Pricing for Revenue Maximization in IoT Data Markets: An Information Design Perspective. In Proceedings of the IEEE INFOCOM 2019—IEEE Conference on Computer Communications, Paris, France, 29 April–2 May 2019 ; pp. 1837–1845.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>This category also discusses the implications of data trading for social, political, economic, and cultural contexts [ 5]. Finally, many articles discuss the topic of exploitation of individual data in personal data marketplaces [ 120–123]. Table 4.
-... [another target-aligned mention] ...
-[102–104] GovernanceExploring governing processes by certain actors (e.g., data marketplace operators) via several mechanisms, such as norms or power.[106–117] Social implications Discussing data marketplace impacts for society. [5,118–123] 3.4. The Finance Domain We identify three categories in the STOF ﬁnance domain (see Table 5).</t>
+          <t>[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
+... [another target-aligned mention] ...
+Res. 2021 ,16 3329 The topics of this category include data trading models that consider contract the- ory [ 128], information design perspective [ 129], and equilibrium pricing mechanism based on Stackelberg game approach [ 130]. Moreover, pricing mechanisms speciﬁcally for per- sonal data are also discussed.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0.5900000000000001</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0.121835</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>range|Discussion|mid|mid</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1428,17 +1265,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>W2942073230-&gt;W2765365501</t>
+          <t>W2934375453-&gt;W2743929098</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Big Data Market Optimization Pricing Model Based on Data Quality</t>
+          <t>Personal Data Market Optimization Pricing Model Based on Privacy Level</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Pricing of Data Products in Data Marketplaces</t>
+          <t>Data pricing strategy based on data quality</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1448,71 +1285,56 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>S. A. Fricker and Y. V . Maksimov, “Pricing of data products in data marketplaces, ” in Proceedings of the International Confer- ence of Software Business ,v o l .3 0 4 ,p p .4 9 – 6 6 ,2 0 1 7 . [ 2 ] Y .J i a o ,P .W a n g,D .N i y a t o ,M .A b uA l s h e i k h ,a n dS .F e n g,“ P r o fi t maximization auction and data management in big data mar- kets, ” in Proceedings of the 2017 IEEE Wireless Communications and Networking Conference, WCNC , pp. 1–6, San Francisco, CA, USA, 2017 . [ 3 ]A .M u s c h a l l e ,F .S t a h l ,A .L a s e r ,a n dG .V o s s e n ,“ P r i c i n g approaches for data markets,” in Proceedings of the Workshop Business Intelligence for the Real Time Enterprise , pp. 129–144, 2012.</t>
+          <t>Yu, H.; Zhang, M. Data pricing strategy based on data quality. Comput. Ind. Eng. 2017 ,112, 1–10. [CrossRef]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>The storage and calculation of big dataare no longer the sole purpose. By using data mining andmachine learning to analyze data, it provides an opportunityto bring about breakthroughs in processing video, images,a n ds p e e c h[ 1 ] .U n f o r t u n a t e l y ,o n l yas m a l la m o u n to fd a t ai scurrently being fully utilized and its use is limited as well. Thereuse of these data can create huge commercial value, whichis the true meaning of big data.
-... [another target-aligned mention] ...
-In other words, we can create anynumber of quality levels based on them. For simplicity, onlythree measures in 𝑄 𝑑are all scaled in interval [0,1] and will be demonstrated here in detail, i.e., accuracy ,completeness, and redundancy . Table 1 [31] contains the metrics, report names, and description definitions for each quality attribute and liststhe calculation formulas.</t>
+          <t>2.3. Customer’s Self-Selection Behavior Analysis In the privacy data pricing optimization model, consumer self-selection behavior analysis [ 18,19] is an important component and foundation. In an actual market environment, customer purchases of data products are complex and can be affected by a variety of factors, such as consumer preferences, interests, and data product prices.
+... [another target-aligned mention] ...
+In this paper, assuming that the consumer is rational, the consumer’s purchase selection behavior for the data product is determined by the utility function of the privacy data. In previous work, most studies assumed that the willingness to pay was a linear function [ 18,20]. However, the linear value function does not accurately capture the estimates of actual data and consumer’s self-selection behavior.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0.5000000000000001</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0.7200000000000001</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1522,17 +1344,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>W2921968831-&gt;W1841962286</t>
+          <t>W3195579788-&gt;W2168402580</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Personal Data Trading Scheme for Data Brokers in IoT Data Marketplaces</t>
+          <t>Data pricing in machine learning pipelines</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>A Priced Public Sensing Framework for Heterogeneous IoT Architectures</t>
+          <t>Query-based data pricing</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1542,69 +1364,70 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>[23]</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>A. E. Al-Fagih, F. M. Al-Turjman, W. M. Alsalih, and H. S. Hassanein, “A priced public sensing framework for heterogeneous iot architectures,” IEEE Transactions on Emerging Topics in Computing, vol. 1, no. 1, pp. 133–147, June 2013.</t>
+          <t>Koutris P, Upadhyaya P, Balazinska M, Howe B, Suciu D (2012) Query-based data pricing. In: Benedikt M, Krötzsch M, Lenzerini M (eds) Proceedings of the 31st ACM SIGMOD-SIGACT-SIGART sympo-sium on principles of database systems, PODS 2012, Scottsdale, AZ, USA, May 20–24, 2012. ACM,pp 167–178. https://doi.org/10.1145/2213556.2213582</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Al-Fagih et al. proposed a data pricing scheme for public sensing framework considering delay, quality of services, and trust factors [23]. Competitive data markets also have been studied.</t>
+          <t>Pricesshould be computed in polynomial time with respect to the number of participants [ 1]o rt h e number of data products [ 17]. In some application scenarios, however, it takes exponential time to compute the pricing functions with desirable properties, such as Shapley fairness [ 37], arbitrage-freeness [ 58], and revenue maximization [ 17]. For example, Koutris et al.
+... [another target-aligned mention] ...
+For example, Koutris et al. [ 58]s h o w that computing arbitrage-free prices of join queries on a relational database is in generalNP-hard. How to efﬁciently determine prices with desirable properties presents technicalchallenges.
+... [another target-aligned mention] ...
+The ﬁrst formal framework for arbitrage-free query-based data pricing was introduced by Koutris et al. [ 58]. The major idea is that a data seller can ﬁrst specify the prices of a few views Vover a database, and then the price of a query bundle Qis decided algorithmically.
+... [another target-aligned mention] ...
+Subsequently, Koutris et al. [ 59] develop a prototype pricing system, QueryMarket, based on the idea [ 58]. They formulate the pricing model as an integer linear program (ILP) with the objective to minimize the total cost of purchased views V p.
+... [another target-aligned mention] ...
+Cong et al. [58] do. By adapting the theoretical results in [ 58], the authors show that the view-based pricing model for linear aggregation queries is NP-hard.
+... [another target-aligned mention] ...
+[58] do. By adapting the theoretical results in [ 58], the authors show that the view-based pricing model for linear aggregation queries is NP-hard. Lin and Kifer [ 65] study arbitrage-free pricing for general data queries.
+... [another target-aligned mention] ...
+The authors point out that the model by Koutris et al. [ 58] has pricing- based arbitrage, that is, the computed prices may leak information about D. Theoretically, they propose an instance-independent pricing function and a delayed pricing function thatare arbitrage-free across all forms.
+... [another target-aligned mention] ...
+Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.
+... [another target-aligned mention] ...
+A data buyerwith a limited budget may not want to purchase many similar data points, as the diversity oftraining data sets is critical to the performance of machine learning models [ 34]. Query-based pricing models [ 58] allow data buyers to only purchase their interested parts of a data set. However, the existing query-based pricing models are only designed for relational data setsin monopoly markets.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1614,7 +1437,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>W3195579788-&gt;W2168402580</t>
+          <t>W3195579788-&gt;W2612128091</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1624,7 +1447,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Query-based data pricing</t>
+          <t>QIRANA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1634,85 +1457,64 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Koutris P, Upadhyaya P, Balazinska M, Howe B, Suciu D (2012) Query-based data pricing. In: Benedikt M, Krötzsch M, Lenzerini M (eds) Proceedings of the 31st ACM SIGMOD-SIGACT-SIGART sympo-sium on principles of database systems, PODS 2012, Scottsdale, AZ, USA, May 20–24, 2012. ACM,pp 167–178. https://doi.org/10.1145/2213556.2213582</t>
+          <t>Deep S, Koutris P (2017b) QIRANA: a framework for scalable query pricing. In: Salihoglu S, Zhou W, Chirkova R, Yang J, Suciu D (eds) Proceedings of the 2017 ACM international conference on 123 Data pricing in machine learning pipelines 1449 management of data, SIGMOD conference 2017, Chicago, IL, USA, May 14–19, 2017. ACM, pp 699–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Pricesshould be computed in polynomial time with respect to the number of participants [ 1]o rt h e number of data products [ 17]. In some application scenarios, however, it takes exponential time to compute the pricing functions with desirable properties, such as Shapley fairness [ 37], arbitrage-freeness [ 58], and revenue maximization [ 17]. For example, Koutris et al.
-... [another target-aligned mention] ...
-For example, Koutris et al. [ 58]s h o w that computing arbitrage-free prices of join queries on a relational database is in generalNP-hard. How to efﬁciently determine prices with desirable properties presents technicalchallenges.
-... [another target-aligned mention] ...
-The ﬁrst formal framework for arbitrage-free query-based data pricing was introduced by Koutris et al. [ 58]. The major idea is that a data seller can ﬁrst specify the prices of a few views Vover a database, and then the price of a query bundle Qis decided algorithmically.
-... [another target-aligned mention] ...
-Subsequently, Koutris et al. [ 59] develop a prototype pricing system, QueryMarket, based on the idea [ 58]. They formulate the pricing model as an integer linear program (ILP) with the objective to minimize the total cost of purchased views V p.
-... [another target-aligned mention] ...
-Cong et al. [58] do. By adapting the theoretical results in [ 58], the authors show that the view-based pricing model for linear aggregation queries is NP-hard.
-... [another target-aligned mention] ...
-[58] do. By adapting the theoretical results in [ 58], the authors show that the view-based pricing model for linear aggregation queries is NP-hard. Lin and Kifer [ 65] study arbitrage-free pricing for general data queries.
-... [another target-aligned mention] ...
-The authors point out that the model by Koutris et al. [ 58] has pricing- based arbitrage, that is, the computed prices may leak information about D. Theoretically, they propose an instance-independent pricing function and a delayed pricing function thatare arbitrage-free across all forms.
-... [another target-aligned mention] ...
-Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.
-... [another target-aligned mention] ...
-A data buyerwith a limited budget may not want to purchase many similar data points, as the diversity oftraining data sets is critical to the performance of machine learning models [ 34]. Query-based pricing models [ 58] allow data buyers to only purchase their interested parts of a data set. However, the existing query-based pricing models are only designed for relational data setsin monopoly markets.</t>
+          <t>In a sell-side marketplace, the arbiter is operatedby a monopoly data seller to sell the single seller’s data products. In literature, sell-sidemarketplaces are considered by pricing models of both general data sets [ 43] and speciﬁc types of data products, such as XML documents [ 108] and data queries on a relational database [ 29]. A buy-side marketplace [ 120] ,a ss h o w ni nF i g .
+... [another target-aligned mention] ...
+Several examples of arbitrage-free pricing functionsare presented, including the weighted coverage function and the Shannon entropy function. Deep and Koutris [ 29] later implement the theoretical framework [ 28] into a real time pricing system, QIRANA, which computes the price of a query bundle Qfrom the view of uncertainty reduction. They assume that a buyer is facing a set of all possible databaseinstances Swith the same schema as the true database instance D.
+... [another target-aligned mention] ...
+QueryMarket [ 59] tracks the purchased views of a customer and avoids charging those views when pricing future queries of the customer. Both[29]a n d[ 75] support history-aware pricing in the same vein as [ 59]. One drawback of these history-based approaches is that the seller must provide reliable storage to keep users’ queryhistory [ 111].
+... [another target-aligned mention] ...
+By tracking coupon status, the data seller guarantees that each coupon will be usedonly once. However, the pricing function has no arbitrage-free guarantee [ 29]. 3.4 Privacy compensation Machine learning models in many areas, like recommendation systems [ 21] and personalized medical treatments [ 72], require a large amount of personal data.
+... [another target-aligned mention] ...
+Such ﬂexibility makes it easier to version raw data products, and enablesmore ﬂexible pricing mechanisms. For example, according to how much information isrevealed, different prices can be assigned to different queries on the same database [ 29]. 123 1442 Z.
+... [another target-aligned mention] ...
+Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0.5346675000000001</t>
+          <t>0.2572499999999999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Result|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
-      <c r="V13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1722,17 +1524,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>W2509511072-&gt;W1994174199</t>
+          <t>W3195579788-&gt;W2743929098</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Understanding rollover data</t>
+          <t>Data pricing in machine learning pipelines</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Smart data pricing: To share or not to share?</t>
+          <t>Data pricing strategy based on data quality</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1742,69 +1544,58 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Y . Jin and Z. Pang, “Smart data pricing: To share or not to share?,” Proc. IEEE Infocom Workshops on Smart Data Pricing , 2014.</t>
+          <t>Yu H, Zhang M (2017) Data pricing strategy based on data quality. Comput Ind Eng 112:1–10. https:// doi.org/10.1016/j.cie.2017.08.008</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>This heterogeneous data usage brings challenges todesigning mobile data plans, as the available monthly dataquotas may not ﬁt different users’ needs. Shared data plans [3]–[6] can help to even out the het- erogeneity in user demands by allowing multiple users anddevices to share one monthly quota of data usage. Taking thisone step further, users can even be allowed to trade leftoverdata with one another in a secondary data market [7]–[9].Thus, heavy users can reduce the likelihood of exceeding theirquotas by sharing or trading data caps with light users.</t>
+          <t>A more comprehensive list of quality criteria is proposedin [106]. Yu and Zhang [ 117] study the problem of trading multiple versions of a data set, constructed by different data quality factors. They assume customers’ demands and maximum acceptableprices of different versions are public.
+... [another target-aligned mention] ...
+Solving the bi-level programming model is NP-hard. Yu and Zhang [ 117] propose a heuristic genetic algorithm to approach it numerically. 123 1426 Z.
+... [another target-aligned mention] ...
+Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0.0273375</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1814,89 +1605,88 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2743929098</t>
+          <t>W3195579788-&gt;W3084177365</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>Data pricing in machine learning pipelines</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Data pricing strategy based on data quality</t>
+          <t>A Survey on Data Pricing: From Economics to Data Science</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Yu, H.; Zhang, M. Data pricing strategy based on data quality. Comput. Ind. Eng. 2017 ,112, 1–10. [CrossRef]</t>
+          <t>Pei J (2020) A survey on data pricing: from economics to data science. IEEE Trans Knowl Data Eng. https://doi.org/10.1109/TKDE.2020.3045927 123 1452 Z. Cong et al.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>[ 62] create efﬁcient query-based auctions by considering both the value data and the resource consumption of queries. Many other articles also propose data quality-based pricing models by considering a bi-level mathematical programming model [ 63], Fair Knapsack Pricing [ 64,65], or optimal distributing algorithm [ 66]. Other works on data quality-based pricing speciﬁcally focus on XML dataset properties [ 67,68].</t>
+          <t>In response to the massive and diversiﬁed demands for various data, data products become valuable assets for purchase and sale. Here, data products refer to data sets as products and information services derived from data sets [ 86]. Data commoditization motivates data owners to share their data products in exchange of rewards and thus helps data buyers to access dataproducts of high quality and large quantities.
+... [another target-aligned mention] ...
+In this article, we try to present acomprehensive survey on data pricing in machine learning pipelines. Very recently, Pei [ 86] presents a survey connecting economics, digital product pricing, and data product pricing. Heidentiﬁes a series of desirable properties in data pricing and reviews the techniques achievingthose properties.
+... [another target-aligned mention] ...
+Heidentiﬁes a series of desirable properties in data pricing and reviews the techniques achievingthose properties. But Pei [ 86] does not focus on machine learning pipeline and does not cover the studies of pricing data labels. The rest of this survey is organized as follows.
+... [another target-aligned mention] ...
+2.4 Desiderata of data pricing There are some desiderata preferred by most pricing models. In this section, we brieﬂy reviewthe six desiderata suggested by Pei [ 86]. In addition, we complement the existing study by an important desideratum, effort elicitation.
+... [another target-aligned mention] ...
+The revenue of a seller is maximizedwhen the manufacturing level is set such that the marginal revenue is zero [ 11]. Since data products can be re-produced at almost zero costs [ 1], the revenue maximization techniques for data products and physical products are quite different [ 86]. Fairness In some scenarios, sellers need to cooperatively participate in a transaction.
+... [another target-aligned mention] ...
+As a consequence, a critical concern is that a data buyer may circumvent theadvertised price of a product through buying a bundle of cheaper ones, which negativelyaffects the seller’s revenue. For example, consider a data seller selling noisy queries to theseller’s database [ 84,86], and the seller perturbs each query answer independently with random noise. An answer with a variance of 5 is sold at $5 and with a variance of 1 is soldat $50.
+... [another target-aligned mention] ...
+Privacy-preservation Privacy protection during the transactions of data raises more and more concerns. In data marketplaces, the privacy of buyers, sellers, and involved third partiesare highly vulnerable, and might be disclosed in many different ways [ 86]. Many different solutions have been proposed for privacy protection in data markets [ 34,47,62].
+... [another target-aligned mention] ...
+7.1 Data pricing models in industry In recent years, many data marketplaces have emerged, where raw and processed data sets, theservices of data labeling, and machine learning models are traded [ 105]. Six pricing models are commonly used in the real-world data marketplaces [ 86,105], namely free data, ﬂat fee tariff model, pay-per-use model, package pricing, two-part tariff model, and freemium. Data marketplaces operated by authorities or non-proﬁt organizations usually provide raw data sets free of charge.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.1714999999999999</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1906,7 +1696,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W2790400697</t>
+          <t>W3084177365-&gt;W2168402580</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1916,7 +1706,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>Query-based data pricing</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1926,19 +1716,21 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>[136]</t>
+          <t>[121]</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>F. Liang, W. Yu, D. An, Q. Yang, X. Fu, and W. Zhao, “A survey on big data market: Pricing, trading and protection,” IEEE Access, vol. PP , pp. 1–1, 02 2018.</t>
+          <t>P . Koutris, P . Upadhyaya, M. Balazinska, B. Howe, and D. Su- ciu, “Query-based data pricing,” in Proceedings of the 31st ACM SIGMOD-SIGACT-SIGAI Symposium on Principles of Database Sys- tems, ser. PODS’12. New York, NY, USA: Association for Computing Machinery, 2012, pp. 167–178.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>For example, Liang et al. [136] survey the life cycle of big data, and reviews 11 data pricing models. They also discuss data trading and protection.
-... [another target-aligned mention] ...
-Very recently, Zhang and Beltr ´an [220] review the state-of-the-art data pricing methods. They categorize data pricing methods according to two important data properties, granularity and privacy, This article covers a substantially broader scope than those [75], [136], [220]. We connect economics, digital product pricing and data product pricing.</t>
+          <t>Each level is modeled as a maximization problem and thus the whole model is a bi-level programming problem, which is NP-hard. Another way to form multiple versions of data products is to charge by queries [121]–[124]. Intuitively, a data seller may treat a view of a data set as a version.
+... [another target-aligned mention] ...
+Koutris et al. [121], [124] propose a framework of query and view based data pricing. The major idea is that a seller only needs to specify the prices on a few views, and then the prices of other views can be decided algorithmically.
+... [another target-aligned mention] ...
+[151] point out that a pricing model charging users a certain amount of API calls for a ﬁxed rate may potentially allow arbitrage, depending on the package size. Arbitrage-freeness is one of the fundamental properties of pricing models in query and view based pricing [121]– [124]. Li and Miklau [134] and Li et al.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1948,49 +1740,34 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.4800000000000001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2000,17 +1777,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>W2942073230-&gt;W2289113545</t>
+          <t>W3084177365-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Big Data Market Optimization Pricing Model Based on Data Quality</t>
+          <t>A Survey on Data Pricing: From Economics to Data Science</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Smart data pricing models for the internet of things: a bundling strategy approach</t>
+          <t>Query-Based Data Pricing</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2020,17 +1797,21 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>[17]</t>
+          <t>[121]</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Y. Bakos and E. Brynjolfsson, “ Aggregation and disaggregation of information goods: Implications for bundling, site licensing,and micropayment systems, ” Lectures in E-Commerce ,p p .1 0 3 – 122, 2001. [ 1 8 ] D .N i y a t o ,D .T .H o a n g ,N .C .L u o n g ,P .W a n g ,D .I .K i m ,a n d Z. Han, “Smart data pricing models for the internet of things:a bundling strategy approach, ” IEEE Network,v o l .3 0 ,n o .2 ,p p . 18–25.</t>
+          <t>P . Koutris, P . Upadhyaya, M. Balazinska, B. Howe, and D. Su- ciu, “Query-based data pricing,” in Proceedings of the 31st ACM SIGMOD-SIGACT-SIGAI Symposium on Principles of Database Sys- tems, ser. PODS’12. New York, NY, USA: Association for Computing Machinery, 2012, pp. 167–178.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>They believe that the two pricingmechanisms of information products, i.e., fixed costand pay-per-payment mechanisms, may affect theprofit of the seller. (2) Bundling pricing: this strategy originates from capital data market, and it represents an aggregation tech-nique [17]. In the capital data market, data vendors Complexity 3 bundle multiple types of products in accordance with certain strategies and allocate different prices forthem to be selected by heterogeneous consumers.Niyato et al.</t>
+          <t>Each level is modeled as a maximization problem and thus the whole model is a bi-level programming problem, which is NP-hard. Another way to form multiple versions of data products is to charge by queries [121]–[124]. Intuitively, a data seller may treat a view of a data set as a version.
+... [another target-aligned mention] ...
+Koutris et al. [121], [124] propose a framework of query and view based data pricing. The major idea is that a seller only needs to specify the prices on a few views, and then the prices of other views can be decided algorithmically.
+... [another target-aligned mention] ...
+[151] point out that a pricing model charging users a certain amount of API calls for a ﬁxed rate may potentially allow arbitrage, depending on the package size. Arbitrage-freeness is one of the fundamental properties of pricing models in query and view based pricing [121]– [124]. Li and Miklau [134] and Li et al.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2040,49 +1821,34 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0.3361999999999999</t>
+          <t>0.4800000000000001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2092,7 +1858,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W2126626399</t>
+          <t>W3084177365-&gt;W2734426755</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2102,7 +1868,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>The Price Is Right</t>
+          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2112,69 +1878,54 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>[192]</t>
+          <t>[223]</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R. Tang, H. Wu, Z. Bao, S. Bressan, and P . Valduriez, “The price is right,” in Database and Expert Systems Applications, H. Decker, L. Lhotsk ´a, S. Link, J. Basl, and A. M. Tjoa, Eds. Berlin, Heidelberg: Springer Berlin Heidelberg, 2013, pp. 380–394.</t>
+          <t>Z. Zheng, Y. Peng, F. Wu, S. Tang, and G. Chen, “An online pricing mechanism for mobile crowdsensing data markets,” in Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing , ser. Mobihoc’17. New York, NY, USA: Association for Computing Machinery, 2017.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Tang et al. [192] follow the view and query based pricing framework and consider each tuple as the the minimum granularity of data. Their model assigns to each tuple a Authorized licensed use limited to: Carleton University.</t>
+          <t>Zheng et al. [223] consider online pricing for mobile crowd-sensing data markets. Different from most of the work on data markets, they assume that data providers are distributed in space and there are three types of spa- tial queries from buyers, namely single-data query (e.g., inquiring the value at a speciﬁc location), multi-data query (e.g., inquiring the mean in a region) and range query (e.g., inquiring the probability that the data at a region falls in a given range).</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.1007999999999999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
-      <c r="V18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2184,17 +1935,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>W2509511072-&gt;W2010653253</t>
+          <t>W2790400697-&gt;W2765365501</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Understanding rollover data</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>A survey of smart data pricing</t>
+          <t>Pricing of Data Products in Data Marketplaces</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2204,69 +1955,54 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[83]</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Surveys (CSUR) , vol. 46, no. 2, p. 15, 2013.</t>
+          <t>S. A. Fricker and Y . V . Maksimov, “Pricing of data products in data marketplaces,” in International Conference of Software Business. Springer, 2017, pp. 49–66.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>I. I NTRODUCTION Most Internet service providers (ISPs) today charge their users a ﬂat fee for a limited amount of mobile data that can be used each month, with steep overage fees for exceeding thismonthly quota [1]. Moreover, in most cases, leftover data atthe end of each month cannot be rolled over into subsequentmonths.</t>
+          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0.0273375</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2276,37 +2012,37 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2916829860</t>
+          <t>W2790400697-&gt;W2743929098</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ARETE: On Designing Joint Online Pricing and Reward Sharing Mechanisms for Mobile Data Markets</t>
+          <t>Data pricing strategy based on data quality</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>grouped</t>
+          <t>high_confidence</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>[82]</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Zheng, Z.; Peng, Y.; Wu, F.; Tang, S.; Chen, G. ARETE: On Designing Joint Online Pricing and Reward Sharing Mechanisms for Mobile Data Markets. IEEE Trans. Mob. Comput. 2020 ,19, 769–787. [CrossRef]</t>
+          <t>H. Yu and M. Zhang, “Data pricing strategy based on data quality,” Computers &amp; Industrial Engineering, vol. 112, pp. 1–10, 2017.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Another algorithm allows data price to be derived from the privacy losses [ 54]. Studies in query-based pricing mechanisms consider many cases such as query interfaces for mobile crowd-sensed data [ 55,56], cloud-based data mar- ketplaces with possibilities to share cloud resources [ 57], spatial data [ 58], aggregated data from multiple distributed system [ 59], and data acquired from Application Programming Interfaces (APIs) [ 60]. Moreover, Tang et al.</t>
+          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2316,49 +2052,34 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0.3285599999999999</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2368,17 +2089,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>W4323644227-&gt;W2612128091</t>
+          <t>W3089176333-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A Survey of Data Pricing for Data Marketplaces</t>
+          <t>Towards Query Pricing on Incomplete Data</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>QIRANA</t>
+          <t>Query-Based Data Pricing</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2388,73 +2109,58 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>[55]</t>
+          <t>[14]</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>——, “Qirana: A framework for scalable query pricing,” in Pro- ceedings of the 2017 ACM International Conference on Management of Data, ser. SIGMOD’17. New York, NY, USA: Association for Computing Machinery, 2017, pp. 699–713.</t>
+          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM, vol. 62, no. 5, p. 43, 2015.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Many theoretical methods are not scalable in practice. Qirana [55], [56] is a system for query-based pricing, which allows data sellers to choose from a set of pricing functions that are information arbitrage-free, which covers both post-processing arbitrage- freeness and serendipitous arbitrage-freeness in Lin and Kifer’s taxonomy [138]. Qirana also supports history-aware pricing.
-... [another target-aligned mention] ...
-If a buyer gets two coupons c1andc2in two different purchases such that c1[(tid;uid;v )] =c2[(tid;uid;v )], then the buyer can ask the seller for a refund by showing the two coupons. As pointed out by Deep and Koutris [55], the refund mechanism does not provide any arbitrage-free guarantee. Qirana [55], [56] can support history-aware pricing.
-... [another target-aligned mention] ...
-As pointed out by Deep and Koutris [55], the refund mechanism does not provide any arbitrage-free guarantee. Qirana [55], [56] can support history-aware pricing. To incorporate a query history, suppose a buyer already purchases queries Q=Q1;:::;Qkand pays for a to- tal ofp(Q;D )so far.</t>
+          <t>p3 2019-10-21 2019-11-01 t4u2? 2019-09-22 ?(c)Product(P) Pid Size Memory Price p14.7 64 $5988 p24.7 256 $7288 p35.5 64 $6888 p45.5 256 $8188 the literature [13], [14], [15], [16], [17], [18], [19]. However, these existing pricing approaches are notsuitable for pricing incomplete data, since they do not consider data complete- ness.
+... [another target-aligned mention] ...
+An arbitrage-free price function means that, the data buyer cannot purchase a query by buying a group of other queries at a lower price, and the price of a given query is unique and same. In particular, the arbitrage-free property is deﬁned based on a notion of query determinacy [14]. Informally, a set of data views/queries V determines some query Q, if one can compute answers of Qonly from answers of views without having access to the underlying dataset.
+... [another target-aligned mention] ...
+The seller sets the price of a speciﬁc set of base queries (also called view), and then, the algorithm has to derive the price of any other query that could be made to the database. This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51].</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2464,17 +2170,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W2734426755</t>
+          <t>W3089176333-&gt;W2612128091</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Data Pricing: From Economics to Data Science</t>
+          <t>Towards Query Pricing on Incomplete Data</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
+          <t>QIRANA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2484,17 +2190,25 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>[223]</t>
+          <t>[16]</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Z. Zheng, Y. Peng, F. Wu, S. Tang, and G. Chen, “An online pricing mechanism for mobile crowdsensing data markets,” in Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing , ser. Mobihoc’17. New York, NY, USA: Association for Computing Machinery, 2017.</t>
+          <t>S. Deep and P. Koutris, “QIRANA: A framework for scalable query pricing,” in SIGMOD, pp. 699–713, 2017.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Zheng et al. [223] consider online pricing for mobile crowd-sensing data markets. Different from most of the work on data markets, they assume that data providers are distributed in space and there are three types of spa- tial queries from buyers, namely single-data query (e.g., inquiring the value at a speciﬁc location), multi-data query (e.g., inquiring the mean in a region) and range query (e.g., inquiring the probability that the data at a region falls in a given range).</t>
+          <t>p3 2019-10-21 2019-11-01 t4u2? 2019-09-22 ?(c)Product(P) Pid Size Memory Price p14.7 64 $5988 p24.7 256 $7288 p35.5 64 $6888 p45.5 256 $8188 the literature [13], [14], [15], [16], [17], [18], [19]. However, these existing pricing approaches are notsuitable for pricing incomplete data, since they do not consider data complete- ness.
+... [another target-aligned mention] ...
+One can also compute other combined prices (e.g., the highest/average price) of lineage tuples for it. Moreover, the higher the tuple completeness, the higher the UCA price.The arbitrage-free property widely explored in relevant studies [13], [16], [19] is a typical and important property for price functions. This property is necessary for data pricing toavoid arbitrage .
+... [another target-aligned mention] ...
+Following existing studies [31], [7], [10], we simulate incomplete datasets via randomly discarding some values at a certain missing rate. In the experiments, following the related work [16], we use 40 queries over four datasets to conduct performance evaluation. All of the queries are described in Table 5, including 16 queries (w.r.t.
+... [another target-aligned mention] ...
+The seller sets the price of a speciﬁc set of base queries (also called view), and then, the algorithm has to derive the price of any other query that could be made to the database. This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51].
+... [another target-aligned mention] ...
+Our proposed pricing scheme iDBPricer belongs to the category. Q IRANA [16], [54], standing the viewpoint of the data buyer, employs the possible world semantic to price relational queries. In addition, there is a series of studies on pricing machine learning tasks [17], [18], [55], pricing-related problems in both advertising markets and labor markets [56], etc.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2504,49 +2218,34 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0.3361999999999999</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="3" t="inlineStr"/>
-      <c r="V22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2556,17 +2255,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>W2942073230-&gt;W2934375453</t>
+          <t>W3089176333-&gt;W2920282816</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Big Data Market Optimization Pricing Model Based on Data Quality</t>
+          <t>Towards Query Pricing on Incomplete Data</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Personal Data Market Optimization Pricing Model Based on Privacy Level</t>
+          <t>Pricing for Revenue Maximization in IoT Data Markets: An Information Design Perspective</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2576,69 +2275,54 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>[23]</t>
+          <t>[44]</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>J. Yang and C. Xing, “Personal data market optimization pricing model based on privacy level,” Info rmation ,v o l .1 0 ,n o .4 ,p .1 2 3 , 2019.</t>
+          <t>W. Mao, Z. Zheng, and F. Wu, “Pricing for revenue maximization in iot data markets: An information design perspective,” in INFO- COM, pp. 1837–1845, 2019.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Yang etal. [23] studied the pricing model of personal privacy data.They proposed a framework to compensate for privacy loss.This method can compensate for privacy loss based on user’spreferences and allow users to control their data throughfinancial means. Through extensive review of the literature, we can con- clude that existing data pricing literature either investigatespublished data pricing methods or studies new approachesthat focus on relevance and privacy.</t>
+          <t>This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51]. In contrast, another kind of pricing scheme considers the tuples of relations as the structural granularity of the pricing function [15], [26], [52], [53].</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0.8999999999999999</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0.54675</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="3" t="inlineStr"/>
-      <c r="V23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2648,17 +2332,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>W2906578628-&gt;W2473283431</t>
+          <t>W2996741051-&gt;W2010653253</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The Internet of Things: A Review of Enabled Technologies and Future Challenges</t>
+          <t>Dynamic Pricing for Revenue Maximization in Mobile Social Data Market With Network Effects</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Data Collection and Wireless Communication in Internet of Things (IoT) Using Economic Analysis and Pricing Models: A Survey</t>
+          <t>A survey of smart data pricing</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2668,93 +2352,58 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[14]</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>N. C. Luong, D. T. Hoang, P. Wang, D. Niyato, D. I. Kim, and Z. Han, “Data collection and wireless communication in internet of things (iot) using economic analysis and pricing models: A survey,” IEEE Commu- nications Surveys &amp; Tutorials, vol. 18, no. 4, pp. 2546–2590, 2016.</t>
+          <t>S. Sen, C. Joe-Wong, S. Ha and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Surveys (CSUR), vol. 46, no. 2, pp. 15–37, 2013.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>INTRODUCTION THE Internet technology has been experiencing consid- erable modiﬁcations since its early times and has turned out to be an imperative transmission framework aiming at everywhere and every time connectivity [1]. The Internet of Things (IoT) is a new concept permitting billions of tiny machines, for example, sensors, to be connected to the Internet [2], [3]. With the Internet growth, IoT has carried out an impressive effect to several ﬁelds and there have been numerous IoT applications employed for enhancing the network operation and users’ quality of experience.
-... [another target-aligned mention] ...
-With the improvement of IoT, several technologies have been introduced [24], which are the main focus of this paper and are discussed in the following sections in detail. Several good surveys have been published on IoT enabled technologies, such as IoT-based smart cities [25], heterogeneous IoT [5], fog computing for IoT [19], data mining for IoT [26], WSN-based data centric IoT [3], IoT- based cellular communications [1], context awareness-based IoT [27], virtual object-based IoT [28], and IoT-based real- time analytics [29]. This survey provides a detailed expla- nation of the mentioned papers in terms of their contribu- tions and future directions for further research.
-... [another target-aligned mention] ...
-Section V draws a sketch of data mining for IoT [26] classiﬁed into four technologies, i.e., clustering, classiﬁcation, frequent patterns, and association rules. Section VI reports the WSN- based data centric IoT [3] with regard to different data aggregation mechanisms. Section VII summarizes the IoT- based cellular communications [1] considering the long term evolution (LTE).
-... [another target-aligned mention] ...
-A smart city contains a num- ber of classiﬁcations of end-users, for example, inhabitants, administration, business associates, and so on. Though, a number of surveys are available on smart cities, such as [3], [31]–[40] discussing different overviews and architectures of smart cities, this portion elaborates the most recent survey [25] on smart cities. The survey in [25] consists of four main phases, which are discussed in the following subsections.
-... [another target-aligned mention] ...
-Citation information: DOI 10.1109/ACCESS.2018.2886601, IEEE Access Ikram Ud Din et al.: IEEE Access TABLE 1. Analysis of presented surveys Survey Reference Scope Smart Cities: IoT Enabling Technolo- gies[25] Data trafﬁc, virtual power plant, emergency sys- tem, health system Heterogeneous IoT [5] Sensing layer, networking layer, cloud computing layer, application layer Fog Computing for IoT [19] Cloud layer, fog layer, device layer Data mining for IoT [26] Clustering, Classiﬁcation, Frequent patterns, Asso- ciation rules WSN-based data centric IoT [3] Data aggregation mechanisms IoT-based cellular communications [1] Long Term Evolution (LTE) Context Awareness-based IoT [27] Applications and middleware solutions Virtual object-based IoT [28] Historical evolution and current features Real-Time analytics based IoT [29] Wireless, wired, and hybrid data centers TABLE 2. Acronyms and their deﬁnitions Acronym Deﬁnition Acronym Deﬁnition BCCH Broadcast Control Channel OT Operation Theater BS Base Station PRACH Physical Random Access Channel CATM UE MTC Category for User Equipment PSNR Peak-Signal-to-Noise-Ratio CCTV Closed-Circuit Television PUCCH Physical Uplink Control Channel CLA Context Lifecycle Approach PUSCH Uplink Shared Channel C-RAN Cloud-Radio Access Network QoS Quality-of-Service CXaaS Context-as-a-Service RAN Radio Access Network DMRS Demodulation Reference Signal RFID Radio-Frequency Identiﬁcation DoS Denial of Service RLC Radio Link Control ELA Enterprise Lifecycle Approach RSU Road Side Unit F-RAN Fog-Radio Access Network SDN Software Deﬁned Network GPS Global Positioning System SRS Sounding Reference Signal H2H Human-to-Human SSE Sum of Squared Errors IOS Internet Operating System SVM Support Vector Machine IoT Internet of Things UII Unique Item Identiﬁcation KDD Knowledge Discovery in Databases V ANET Vehicular Ad hoc Network LAN Local Area Network VNI Visual Networking Index LSVM Linear Support Vector Machine VPP Virtual Power Plant LTE Long Term Evolution WSN Wireless Sensor Network MTC Machine Type Communication 3GPP 3rd Generation Partnership Project M2M Machine-to-Machine 4G Fourth Generation NB Narrowband 5G Fifth Generation analyzed and distributed for a safer drive.
-... [another target-aligned mention] ...
-Various IoT paradigms have been proposed in the litera- ture [164]–[167], which provide sufﬁcient knowledge about the stated characteristics. The WSN-based data centric IoT survey [3] focuses on the following four issues: i) Data exchange, ii) Resource and task allocation, iii) Coverage and target tracking, and iv) Denial of service (DoS) attack prevention pertaining to economic models. These modules are discussed in the following subsections in detail.
-... [another target-aligned mention] ...
-(c) Data collection in a sealed-bid reverse auction. (d) Data collection, where the service provider splits the budget and the targeted work into various small budgets and periods [3]. A.
-... [another target-aligned mention] ...
-XI. LESSONS LEARNED This section is based on the following IoT-related papers: i) smart cities [25] that consist of trafﬁc management, virtual power plants, emergency and health systems; ii) heteroge- neous IoT [5] that elaborates the functions of application, cloud, networking, and sensing layers; iii) fog computing [19], which elucidates the functionalities of cloud, fog, and device layers; iv) data mining [26], which is classiﬁed into four parts, i.e., clustering, classiﬁcation, frequent patterns, and association rules; v) data centric WSN [3] with respect to four aggregated schemes, i.e., data exchange, task and/or re- source allocation, sensing coverage with target identiﬁcation, and prevention of DoS attacks; vi) cellular communications [1] with regard to LTE; vii) content-awareness [27], which delineates a range of middleware applications along with their solutions; viii) virtual objects [28] in terms of archi- tectures and their roles; and ix) real-time analytics [29] with respect to network requirements and methodologies. These lessons are presented in the following subsections in detail.
-... [another target-aligned mention] ...
-E. WSN-BASED DATA CENTRIC IOT Different from the traditional WSN, the IoT-based WSN [3] needs to be smarter [163], because it does not only execute ordinary tasks but also perform important functions with little human involvement. Dealing with billions of IoT devices, numerous challenges in terms of economical deployment and appropriate processing can be faced.
-... [another target-aligned mention] ...
-Data mining for IoT [26] Presents an overview of the features of data mining for IoT in line with future challenges and open issues.Ignores to present the IoT overview from various angles, such as semantics, devices, and Internet. WSN-based data centric IoT [3] Studies various functions of the economic and pricing prototypes, called intelligent log- ical decision-making techniques, to design procedures and systems for wireless sensor networks.Lakes to provide a partition of network trafﬁc into logical phases that affect the functionali- ties of WSNs. IoT-based cellular communications [1] Delivers a detailed explanation of the MTC development through various LTE releases and the newly designed MTC categories.Discusses only the physical layer features and neglects other important aspects, such as end- to-end network slicing and scalability issues for mobile IoT.
-... [another target-aligned mention] ...
-Real-Time analytics based IoT [29] Deﬁnes the essentials of the real-time IoT analytics and procedures, and clariﬁes limi- tations of the system policies for their valida- tion.Does not discuss protocols and applications that would assist the research community to choose appropriate technologies. with respect to WSN, WiFi, and cellular communications, iii) fog computing [19] with regard to users’ privacy and trust- worthiness, iv) data mining [26] in line with decentralized and heterogeneous techniques, v) data centric WSN [3] con- cerning mobility patterns and payment security, vi) cellular communications [1] with reference to obtaining frequency and operating cell IDs, vii) context-awareness [27] pertaining to device recognition and connection, viii) virtual objects [28] regarding their lifecycle and garbage collection, and ix) real-time analytics [29] in connection with scalability, fault tolerance, and massive data transmission. These challenges are addressed in the following subsections separately.
-... [another target-aligned mention] ...
-Pricing models for determining communica- tions and data gathering glitches in delivery networksLuonget al. [3] have provided economic models to determine communications and data aggregation issues in the IoT environment. Long Term Evolution (LTE-A)-based delivery networksElsaadany et al.
-... [another target-aligned mention] ...
-Hence, the server should keep track of the pattern of mobility of each in- dividual cellphone user [308]. In addition, payment security and bids’ conﬁdentiality [309] are two other prominent open research issues [3]. F.</t>
+          <t>However, this issue has been largely neglected by the network operators in the literature. To obtain greater revenue, the network operators can adopt appropriate pricing strategies to directly affect the users’ demand [14]. Initially, the operator only used static pricing that is simple ﬂat-rate data plans to engage users.
+... [another target-aligned mention] ...
+The motivation or intuition is that pricing should be leveraged strategically to affect demand to better handle unexploited capacity, hence yielding more revenue [15]. For example, MTN in Uganda and Uninor in India have offered time-dependent pricing for mobile message, where the message price is dynamically changed after one day or even one hour to achieve balance between the supply and demand [14], [16]. Also, China Telecom charges its users a discount data fees during less congested times, e.g., at night, and normal data fees otherwise.
+... [another target-aligned mention] ...
+II. R ELATED WORK A group of literature related to our work is the data pricing scheme for the network operators, which is designed to offer proﬁtable business as well as to create favorable services for the users [14], [21]. The network operators have been experiencing several emerging and innovative data pricing schemes, e.g., rollover data plans, secondary data market scheme [22] and sponsored data plan [23], [24].</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0.6091875</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr"/>
-      <c r="U24" s="3" t="inlineStr"/>
-      <c r="V24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2764,17 +2413,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>W4323644227-&gt;W2168402580</t>
+          <t>W2473283431-&gt;W2180742472</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>A Survey of Data Pricing for Data Marketplaces</t>
+          <t>Data Collection and Wireless Communication in Internet of Things (IoT) Using Economic Analysis and Pricing Models: A Survey</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Query-based data pricing</t>
+          <t>Smart data pricing</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2784,21 +2433,21 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>[121]</t>
+          <t>[30]</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>P . Koutris, P . Upadhyaya, M. Balazinska, B. Howe, and D. Su- ciu, “Query-based data pricing,” in Proceedings of the 31st ACM SIGMOD-SIGACT-SIGAI Symposium on Principles of Database Sys- tems, ser. PODS’12. New York, NY, USA: Association for Computing Machinery, 2012, pp. 167–178.</t>
+          <t>D. Niyato, X. Lu, P. Wang, D. I. Kim, and Z. Han, “Economics of internet of things (iot): An information market approach,” arXiv preprint arXiv:1510.06837, 2015.[31] D. Niyato, D. T. Hoang, N. C. Luong, P. Wang, D. I. Kim, and Z. Han, “Smart data pricing models for internet-of-things (iot): A bundling strategy approach,” vol. 30, no. 2, pp. 18–25, 2016.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Each level is modeled as a maximization problem and thus the whole model is a bi-level programming problem, which is NP-hard. Another way to form multiple versions of data products is to charge by queries [121]–[124]. Intuitively, a data seller may treat a view of a data set as a version.
-... [another target-aligned mention] ...
-Koutris et al. [121], [124] propose a framework of query and view based data pricing. The major idea is that a seller only needs to specify the prices on a few views, and then the prices of other views can be decided algorithmically.
-... [another target-aligned mention] ...
-[151] point out that a pricing model charging users a certain amount of API calls for a ﬁxed rate may potentially allow arbitrage, depending on the package size. Arbitrage-freeness is one of the fundamental properties of pricing models in query and view based pricing [121]– [124]. Li and Miklau [134] and Li et al.</t>
+          <t>Location-based services are also primary services of the IoT with an expected revenue of $34.8 billion in 2020 (http://iotbusinessnews.com). Among these resources, the sensing data and information are the most important ones in IoT since they can maximize the utility and proﬁt of owners and providers [30]. To describe how IoT changes business models, an IoT business model (see Fig.
+... [another target-aligned mention] ...
+The information can be treated as items traded in the market, and the main problem is how to set prices for the sensing infor- mation so that the service providers’ proﬁts are maximized. Consider a competitive market involving IoT service providers, the authors in [30] formulated the competition in setting the price as a non-cooperative game. The players are the service providers, i.e., sellers, and the strategy of each player is to set the price of the sensing information to maximize his own payoff, i.e., proﬁt.
+... [another target-aligned mention] ...
+The seller ﬁnds optimal rate and charge for the buyers through the utility functionMaximized throughput, load balance, and minimized costOptimization solution 6) Collusion and Price of Anarchy: In a competitive mar- ket, service providers set selling prices to maximize their own proﬁts given the strategies of other providers. A Nash equilibrium can be an appropriate solution as proposed in [30]. However, due to selﬁsh behaviors of the service providers, they can collude with each other to optimize their proﬁts collectively, and thus the Nash equilibrium become inefﬁcient [274].</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2808,49 +2457,34 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr"/>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2860,17 +2494,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>W4323644227-&gt;W2765365501</t>
+          <t>W2790400697-&gt;W2168402580</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A Survey of Data Pricing for Data Marketplaces</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Pricing of Data Products in Data Marketplaces</t>
+          <t>Query-based data pricing</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2880,71 +2514,54 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>[75]</t>
+          <t>[76]</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>S. A. Fricker and Y. V . Maksimov, “Pricing of data products in data marketplaces,” in Software Business, A. Ojala, H. Holm-str¨om Olsson, and K. Werder, Eds. Cham: Springer International Publishing, 2017, pp. 49–66.</t>
+          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM (JACM), vol. 62, no. 5, p. 43, 2015.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>They also discuss data trading and protection. Fricker and Maksimov [75] report a literature survey over 18 research articles regarding several research questions, including maturity of the pric- ing models. Very recently, Zhang and Beltr ´an [220] review the state-of-the-art data pricing methods.
-... [another target-aligned mention] ...
-Very recently, Zhang and Beltr ´an [220] review the state-of-the-art data pricing methods. They categorize data pricing methods according to two important data properties, granularity and privacy, This article covers a substantially broader scope than those [75], [136], [220]. We connect economics, digital product pricing and data product pricing.</t>
+          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
       <c r="R26" s="3" t="inlineStr"/>
       <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2954,17 +2571,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>W4323644227-&gt;W2734426755</t>
+          <t>W2790400697-&gt;W2289113545</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>A Survey of Data Pricing for Data Marketplaces</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
+          <t>Smart data pricing models for the internet of things: a bundling strategy approach</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2974,69 +2591,54 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>[223]</t>
+          <t>[77]</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Z. Zheng, Y. Peng, F. Wu, S. Tang, and G. Chen, “An online pricing mechanism for mobile crowdsensing data markets,” in Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing , ser. Mobihoc’17. New York, NY, USA: Association for Computing Machinery, 2017.</t>
+          <t>D. Niyato, D. T. Hoang, N. C. Luong, P. Wang, D. I. Kim, and Z. Han, “Smart data pricing models for the Internet of Things: A bundling strategy approach,” IEEE Network, vol. 30, no. 2, pp. 18–25, 2016.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Zheng et al. [223] consider online pricing for mobile crowd-sensing data markets. Different from most of the work on data markets, they assume that data providers are distributed in space and there are three types of spa- tial queries from buyers, namely single-data query (e.g., inquiring the value at a speciﬁc location), multi-data query (e.g., inquiring the mean in a region) and range query (e.g., inquiring the probability that the data at a region falls in a given range).</t>
+          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0.3361999999999999</t>
+          <t>0.1399999999999999</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
       <c r="R27" s="3" t="inlineStr"/>
       <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3046,12 +2648,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>W4319769514-&gt;W2293940046</t>
+          <t>W2790400697-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Data-Driven Learning for Data Rights, Data Pricing, and Privacy Computing</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3066,17 +2668,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[76]</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Koutris P, Upadhyaya P, Balazinska M, Howe B, Suciu D. Query-based data pricing. J ACM 2015;62(5):1–44 .</t>
+          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM (JACM), vol. 62, no. 5, p. 43, 2015.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Koutris et al. [25] transformed the query-based pricing problem into a network ﬂow problem and automatically derived the price of any query from the price of a given set of views. After that, they adopted a dif- ferent perspective, which transformed the query-based pricing problem into optimized integer linear programming, priced the structured query language (SQL) query based on the price point speciﬁed by the seller, and used the query history to avoid the repeated charging of overlapping information [26].</t>
+          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3086,49 +2688,34 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0.8999999999999999</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0.54675</t>
+          <t>0.2339999999999999</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
       <c r="R28" s="3" t="inlineStr"/>
       <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3138,17 +2725,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>W4210813858-&gt;W2293940046</t>
+          <t>W2790400697-&gt;W2473283431</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Query-Based Data Pricing</t>
+          <t>Data Collection and Wireless Communication in Internet of Things (IoT) Using Economic Analysis and Pricing Models: A Survey</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3158,17 +2745,19 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>[26]</t>
+          <t>[56]</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, ``Query- based data pricing,'' J. ACM, vol. 62, no. 5, pp. 144, Nov. 2015.</t>
+          <t>N. C. Luong, D. T. Hoang, P. Wang, D. Niyato, D. I. Kim, and Z. Han, “Data collection and wireless communication in Internet of Things (IoT) using economic analysis and pricing models: a survey,” IEEE Communications Surveys &amp; Tutorials, vol. 18, no. 4, pp. 2546–2590, 2016.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Then data buyers submit queries to the platform, and the platform generates the objective function and corresponding constraints, forming an ILP problem to get the prices. Researchers improved their studies and proposed a framework that allows the price of any query to be derived automatically [26]. QIRANA pricing sys- tem [27] allows exible pricing by allowing the data owners to choose from a variety of pricing functions, specify relation and attribute-level parameters to control the prices of queries.</t>
+          <t>Pricing mechanisms adjust price and payment schedule to guarantee the enough scale of participants and improve the data service, data accuracy, and data coverage. There are several different pricing strategies for evaluating cost according to the different scenarios [56]. The most common strategy is economic-based pricing, which establishes the price model based on economic principles.
+... [another target-aligned mention] ...
+The payoff result will be affected not only by one play, but also by others [63]. In [56] and [64], the authors designed a pricing model to evaluate IoT sensing data. In the model, all vendors sell their data in a competitive manner, and they deﬁne this model as non-cooperative game.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3178,49 +2767,34 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
       <c r="R29" s="3" t="inlineStr"/>
       <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3230,17 +2804,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>W2942073230-&gt;W2293940046</t>
+          <t>W2790400697-&gt;W2734426755</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Big Data Market Optimization Pricing Model Based on Data Quality</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Query-Based Data Pricing</t>
+          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3250,69 +2824,54 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>[21]</t>
+          <t>[75]</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P . Koutris, P . Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing, ” in Proceedings of the Symposium on Principles of Database Systems ,v o l .6 2 ,p p .1 6 7 – 1 7 8 ,2 0 1 2 . [ 2 2 ]Y .S h e n ,B .G u o ,Y .S h e n ,X .D u a n ,X .D o n g ,a n dH .Z h a n g , “ A pricing model for Big Personal Data, ” Tsinghua Science and Technology ,v o l .2 1 ,n o .5 ,p p .4 8 2 – 4 9 0 ,2 0 1 6 .</t>
+          <t>Z. Zheng, Y . Peng, F. Wu, S. Tang, and G. Chen, “An online pricing mechanism for mobile crowdsensing data markets,” in Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing. ACM, 2017, p. 26.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Th e r ea r ea l s os o m es c h o l a r sw h oh a v es t u d i e dt h e pricing model of data products from different perspectives.Koutris et al. [21] studied query-based pricing, and theydesigned a pricing algorithm that satisfies no-arbitrage andno-discount allowing the price of any query to be exportedautomatically. Shen et al.</t>
+          <t>Citation information: DOI 10.1109/ACCESS.2018.2806881, IEEE Access 11 TABLE II: Data pricing models Ref. Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.2339999999999999</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
       <c r="R30" s="3" t="inlineStr"/>
       <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -3322,93 +2881,76 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>W3089176333-&gt;W2293940046</t>
+          <t>W4226305897-&gt;W2533772775</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Towards Query Pricing on Incomplete Data</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Query-Based Data Pricing</t>
+          <t>A pricing model for Big Personal Data</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>[14]</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM, vol. 62, no. 5, p. 43, 2015.</t>
+          <t>Yuncheng, S.; Bing, G.; Yan, S.; Xuliang, D.; Xiangqian, D.; Hong, Z. A pricing model for Big Personal Data. Tsinghua Sci. Technol. 2016 ,21, 482–490. [CrossRef]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>p3 2019-10-21 2019-11-01 t4u2? 2019-09-22 ?(c)Product(P) Pid Size Memory Price p14.7 64 $5988 p24.7 256 $7288 p35.5 64 $6888 p45.5 256 $8188 the literature [13], [14], [15], [16], [17], [18], [19]. However, these existing pricing approaches are notsuitable for pricing incomplete data, since they do not consider data complete- ness.
-... [another target-aligned mention] ...
-An arbitrage-free price function means that, the data buyer cannot purchase a query by buying a group of other queries at a lower price, and the price of a given query is unique and same. In particular, the arbitrage-free property is deﬁned based on a notion of query determinacy [14]. Informally, a set of data views/queries V determines some query Q, if one can compute answers of Qonly from answers of views without having access to the underlying dataset.
-... [another target-aligned mention] ...
-The seller sets the price of a speciﬁc set of base queries (also called view), and then, the algorithm has to derive the price of any other query that could be made to the database. This group consists of pricing generalized chain queries (i.e., a special type of join conjunctive query when the base queries are only selection queries) [14], [42] and pricing SQL queries [13], [16]. There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51].</t>
+          <t>[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
+... [another target-aligned mention] ...
+[ 131] propose pricing functions for aggregated personal data; Parra-Arnau [ 132] mathematically examine the tradeoff between privacy and money in personal data market; Yuncheng et al. [ 133] identify the properties that contribute to price personal data, such as data cost, value weight, information entropy, credit rating, and data reference index; Li et al. [ 134,135], discuss an economic theory of pricing personal data.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0.009025</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
       <c r="R31" s="3" t="inlineStr"/>
       <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
-      <c r="U31" s="3" t="inlineStr"/>
-      <c r="V31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3418,17 +2960,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>W2790400697-&gt;W2293940046</t>
+          <t>W3021125948-&gt;W2010653253</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>Contract Design in Hierarchical Game for Sponsored Content Service Market</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Query-Based Data Pricing</t>
+          <t>A survey of smart data pricing</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3438,17 +2980,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>[76]</t>
+          <t>[35]</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM (JACM), vol. 62, no. 5, p. 43, 2015.</t>
+          <t>S. Sen, C. Joe-Wong, S. Ha and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” Acm computing surveys (csur), vol. 46, no. 2, pp. 15, 2013.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
+          <t>Thus, the MNO determines the optimal price pto solve the following payoff, i.e., utility, maximization problem: UMNO (p) =XN i=1i[(1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3458,49 +3000,34 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0.8999999999999999</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0.54675</t>
+          <t>0.0675</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
       <c r="R32" s="3" t="inlineStr"/>
       <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -3510,12 +3037,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>W3195579788-&gt;W2765365501</t>
+          <t>W2942073230-&gt;W2765365501</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Data pricing in machine learning pipelines</t>
+          <t>Big Data Market Optimization Pricing Model Based on Data Quality</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3530,71 +3057,56 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Fricker SA, Maksimov YV (2017) Pricing of data products in data marketplaces. In: Ojala A, Holmström Olsson H, Werder K (eds) Software business. Springer, Cham, pp 49–66</t>
+          <t>S. A. Fricker and Y. V . Maksimov, “Pricing of data products in data marketplaces, ” in Proceedings of the International Confer- ence of Software Business ,v o l .3 0 4 ,p p .4 9 – 6 6 ,2 0 1 7 . [ 2 ] Y .J i a o ,P .W a n g,D .N i y a t o ,M .A b uA l s h e i k h ,a n dS .F e n g,“ P r o fi t maximization auction and data management in big data mar- kets, ” in Proceedings of the 2017 IEEE Wireless Communications and Networking Conference, WCNC , pp. 1–6, San Francisco, CA, USA, 2017 . [ 3 ]A .M u s c h a l l e ,F .S t a h l ,A .L a s e r ,a n dG .V o s s e n ,“ P r i c i n g approaches for data markets,” in Proceedings of the Workshop Business Intelligence for the Real Time Enterprise , pp. 129–144, 2012.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Figure 1shows the connections of the four tasks. There are some previous surveys related to data pricing [ 35,63,120]. This article covers a substantially deeper and more focused scope than those.
-... [another target-aligned mention] ...
-2.3 Four types of data markets Similar to physical goods, the prices of data products are also inﬂuenced by the dominanceand diversity of supplies and demands in the market. Fricker and Maksimov [ 35] identify four types of data markets. First, in a monopoly ,a supplier holds enough market power to set prices to maximize proﬁts.</t>
+          <t>The storage and calculation of big dataare no longer the sole purpose. By using data mining andmachine learning to analyze data, it provides an opportunityto bring about breakthroughs in processing video, images,a n ds p e e c h[ 1 ] .U n f o r t u n a t e l y ,o n l yas m a l la m o u n to fd a t ai scurrently being fully utilized and its use is limited as well. Thereuse of these data can create huge commercial value, whichis the true meaning of big data.
+... [another target-aligned mention] ...
+In other words, we can create anynumber of quality levels based on them. For simplicity, onlythree measures in 𝑄 𝑑are all scaled in interval [0,1] and will be demonstrated here in detail, i.e., accuracy ,completeness, and redundancy . Table 1 [31] contains the metrics, report names, and description definitions for each quality attribute and liststhe calculation formulas.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0.7200000000000001</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0.0293999999999999</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Introduction|low|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
       <c r="R33" s="3" t="inlineStr"/>
       <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="3" t="inlineStr"/>
-      <c r="V33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3604,7 +3116,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>W2921968831-&gt;W2533772775</t>
+          <t>W2921968831-&gt;W2759182208</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3614,7 +3126,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>A pricing model for Big Personal Data</t>
+          <t>Pricing privacy – the right to know the value of your personal data</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3624,69 +3136,62 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>[30]</t>
+          <t>[18]</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Y . Shen, B. Guo, Y . Shen, X. Duan, X. Dong, and H. Zhang, “A pricing model for Big Personal Data,” Tsinghua Science and Technology, vol. 21, no. 5, pp. 482–490, 2016.</t>
+          <t>G. Malgieri and B. Custers, “Pricing privacy – the right to know the value of your personal data,” Computer Law &amp; Security Review, vol. 34, no. 2, pp. 289 – 303, 2018.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Shen et al. also proposed a linear function based the per- sonal data pricing scheme by considering information entropy, credit of data providers, and data reference index [30]. Xu et al.proposed a dynamic personal data pricing scheme using the multi-armed bandit approach under privacy-preserved personal data environments [31].</t>
+          <t>The pro- posed WTB is also designed based on literature [17] to reﬂect real-world behaviors. This paper also proposes a personal data quality model for the collection of heterogeneous types of personal data by considering correlations of multiple personal data types as well as quantity of personal dataset based on literature [18] related to personal data pricing factors. The correlation of multiple personal data types is important to measure quality of personal dataset because when personal data is combined with other personal data, per- sonal data providers can potentially be identiﬁed through additional processing.
+... [another target-aligned mention] ...
+Content may change prior to final publication. Citation information: DOI 10.1109/ACCESS.2019.2904248, IEEE Access SUBMITTED TO IEEE ACCESS 3 and valuations of privacy (i.e., personal data pricing or pri- vacy pricing models) have also been studied [18], [28]–[33]. Malgieri and Custers investigated that the monetary value of personal data can be quantiﬁed with various personal data pricing factors [18].
+... [another target-aligned mention] ...
+Citation information: DOI 10.1109/ACCESS.2019.2904248, IEEE Access SUBMITTED TO IEEE ACCESS 3 and valuations of privacy (i.e., personal data pricing or pri- vacy pricing models) have also been studied [18], [28]–[33]. Malgieri and Custers investigated that the monetary value of personal data can be quantiﬁed with various personal data pricing factors [18]. Gkatzelis et al.
+... [another target-aligned mention] ...
+Quantifying the value and quality of personal data is an important factor to decide price of personal data. We choose several metrics to deﬁne the personal data quality function Q based on [18]. By analyzing various privacy regulations and researches, this work investigated privacy pricing factors as follows: sizeof dataset, completeness of dataset, a number of data types and their combinations, the level of identiﬁability of personal data.
+... [another target-aligned mention] ...
+There are many possible ways to increase the possibility for market participation of personal data providers; and in this paper, we have focused on a possible approach with personal data providers’ incentives. Since personal data now become a new ﬁnancial asset for individuals [10], this approach also has investigated in previous works [18], [28], [33]. However, it was still ambiguous about the feasibility of the IoT data market with personal data providers’ incentives; in other words, how 2169-3536 (c) 2018 IEEE.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0.0379215</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
       <c r="R34" s="3" t="inlineStr"/>
       <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3696,19 +3201,19 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>W2473283431-&gt;W2180742472</t>
+          <t>W2906578628-&gt;W2473283431</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>The Internet of Things: A Review of Enabled Technologies and Future Challenges</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Data Collection and Wireless Communication in Internet of Things (IoT) Using Economic Analysis and Pricing Models: A Survey</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Smart data pricing</t>
-        </is>
-      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>high_confidence</t>
@@ -3716,73 +3221,78 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>[30]</t>
+          <t>[3]</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>D. Niyato, X. Lu, P. Wang, D. I. Kim, and Z. Han, “Economics of internet of things (iot): An information market approach,” arXiv preprint arXiv:1510.06837, 2015.[31] D. Niyato, D. T. Hoang, N. C. Luong, P. Wang, D. I. Kim, and Z. Han, “Smart data pricing models for internet-of-things (iot): A bundling strategy approach,” vol. 30, no. 2, pp. 18–25, 2016.</t>
+          <t>N. C. Luong, D. T. Hoang, P. Wang, D. Niyato, D. I. Kim, and Z. Han, “Data collection and wireless communication in internet of things (iot) using economic analysis and pricing models: A survey,” IEEE Commu- nications Surveys &amp; Tutorials, vol. 18, no. 4, pp. 2546–2590, 2016.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Location-based services are also primary services of the IoT with an expected revenue of $34.8 billion in 2020 (http://iotbusinessnews.com). Among these resources, the sensing data and information are the most important ones in IoT since they can maximize the utility and proﬁt of owners and providers [30]. To describe how IoT changes business models, an IoT business model (see Fig.
-... [another target-aligned mention] ...
-The information can be treated as items traded in the market, and the main problem is how to set prices for the sensing infor- mation so that the service providers’ proﬁts are maximized. Consider a competitive market involving IoT service providers, the authors in [30] formulated the competition in setting the price as a non-cooperative game. The players are the service providers, i.e., sellers, and the strategy of each player is to set the price of the sensing information to maximize his own payoff, i.e., proﬁt.
-... [another target-aligned mention] ...
-The seller ﬁnds optimal rate and charge for the buyers through the utility functionMaximized throughput, load balance, and minimized costOptimization solution 6) Collusion and Price of Anarchy: In a competitive mar- ket, service providers set selling prices to maximize their own proﬁts given the strategies of other providers. A Nash equilibrium can be an appropriate solution as proposed in [30]. However, due to selﬁsh behaviors of the service providers, they can collude with each other to optimize their proﬁts collectively, and thus the Nash equilibrium become inefﬁcient [274].</t>
+          <t>INTRODUCTION THE Internet technology has been experiencing consid- erable modiﬁcations since its early times and has turned out to be an imperative transmission framework aiming at everywhere and every time connectivity [1]. The Internet of Things (IoT) is a new concept permitting billions of tiny machines, for example, sensors, to be connected to the Internet [2], [3]. With the Internet growth, IoT has carried out an impressive effect to several ﬁelds and there have been numerous IoT applications employed for enhancing the network operation and users’ quality of experience.
+... [another target-aligned mention] ...
+With the improvement of IoT, several technologies have been introduced [24], which are the main focus of this paper and are discussed in the following sections in detail. Several good surveys have been published on IoT enabled technologies, such as IoT-based smart cities [25], heterogeneous IoT [5], fog computing for IoT [19], data mining for IoT [26], WSN-based data centric IoT [3], IoT- based cellular communications [1], context awareness-based IoT [27], virtual object-based IoT [28], and IoT-based real- time analytics [29]. This survey provides a detailed expla- nation of the mentioned papers in terms of their contribu- tions and future directions for further research.
+... [another target-aligned mention] ...
+Section V draws a sketch of data mining for IoT [26] classiﬁed into four technologies, i.e., clustering, classiﬁcation, frequent patterns, and association rules. Section VI reports the WSN- based data centric IoT [3] with regard to different data aggregation mechanisms. Section VII summarizes the IoT- based cellular communications [1] considering the long term evolution (LTE).
+... [another target-aligned mention] ...
+A smart city contains a num- ber of classiﬁcations of end-users, for example, inhabitants, administration, business associates, and so on. Though, a number of surveys are available on smart cities, such as [3], [31]–[40] discussing different overviews and architectures of smart cities, this portion elaborates the most recent survey [25] on smart cities. The survey in [25] consists of four main phases, which are discussed in the following subsections.
+... [another target-aligned mention] ...
+Citation information: DOI 10.1109/ACCESS.2018.2886601, IEEE Access Ikram Ud Din et al.: IEEE Access TABLE 1. Analysis of presented surveys Survey Reference Scope Smart Cities: IoT Enabling Technolo- gies[25] Data trafﬁc, virtual power plant, emergency sys- tem, health system Heterogeneous IoT [5] Sensing layer, networking layer, cloud computing layer, application layer Fog Computing for IoT [19] Cloud layer, fog layer, device layer Data mining for IoT [26] Clustering, Classiﬁcation, Frequent patterns, Asso- ciation rules WSN-based data centric IoT [3] Data aggregation mechanisms IoT-based cellular communications [1] Long Term Evolution (LTE) Context Awareness-based IoT [27] Applications and middleware solutions Virtual object-based IoT [28] Historical evolution and current features Real-Time analytics based IoT [29] Wireless, wired, and hybrid data centers TABLE 2. Acronyms and their deﬁnitions Acronym Deﬁnition Acronym Deﬁnition BCCH Broadcast Control Channel OT Operation Theater BS Base Station PRACH Physical Random Access Channel CATM UE MTC Category for User Equipment PSNR Peak-Signal-to-Noise-Ratio CCTV Closed-Circuit Television PUCCH Physical Uplink Control Channel CLA Context Lifecycle Approach PUSCH Uplink Shared Channel C-RAN Cloud-Radio Access Network QoS Quality-of-Service CXaaS Context-as-a-Service RAN Radio Access Network DMRS Demodulation Reference Signal RFID Radio-Frequency Identiﬁcation DoS Denial of Service RLC Radio Link Control ELA Enterprise Lifecycle Approach RSU Road Side Unit F-RAN Fog-Radio Access Network SDN Software Deﬁned Network GPS Global Positioning System SRS Sounding Reference Signal H2H Human-to-Human SSE Sum of Squared Errors IOS Internet Operating System SVM Support Vector Machine IoT Internet of Things UII Unique Item Identiﬁcation KDD Knowledge Discovery in Databases V ANET Vehicular Ad hoc Network LAN Local Area Network VNI Visual Networking Index LSVM Linear Support Vector Machine VPP Virtual Power Plant LTE Long Term Evolution WSN Wireless Sensor Network MTC Machine Type Communication 3GPP 3rd Generation Partnership Project M2M Machine-to-Machine 4G Fourth Generation NB Narrowband 5G Fifth Generation analyzed and distributed for a safer drive.
+... [another target-aligned mention] ...
+Various IoT paradigms have been proposed in the litera- ture [164]–[167], which provide sufﬁcient knowledge about the stated characteristics. The WSN-based data centric IoT survey [3] focuses on the following four issues: i) Data exchange, ii) Resource and task allocation, iii) Coverage and target tracking, and iv) Denial of service (DoS) attack prevention pertaining to economic models. These modules are discussed in the following subsections in detail.
+... [another target-aligned mention] ...
+(c) Data collection in a sealed-bid reverse auction. (d) Data collection, where the service provider splits the budget and the targeted work into various small budgets and periods [3]. A.
+... [another target-aligned mention] ...
+XI. LESSONS LEARNED This section is based on the following IoT-related papers: i) smart cities [25] that consist of trafﬁc management, virtual power plants, emergency and health systems; ii) heteroge- neous IoT [5] that elaborates the functions of application, cloud, networking, and sensing layers; iii) fog computing [19], which elucidates the functionalities of cloud, fog, and device layers; iv) data mining [26], which is classiﬁed into four parts, i.e., clustering, classiﬁcation, frequent patterns, and association rules; v) data centric WSN [3] with respect to four aggregated schemes, i.e., data exchange, task and/or re- source allocation, sensing coverage with target identiﬁcation, and prevention of DoS attacks; vi) cellular communications [1] with regard to LTE; vii) content-awareness [27], which delineates a range of middleware applications along with their solutions; viii) virtual objects [28] in terms of archi- tectures and their roles; and ix) real-time analytics [29] with respect to network requirements and methodologies. These lessons are presented in the following subsections in detail.
+... [another target-aligned mention] ...
+E. WSN-BASED DATA CENTRIC IOT Different from the traditional WSN, the IoT-based WSN [3] needs to be smarter [163], because it does not only execute ordinary tasks but also perform important functions with little human involvement. Dealing with billions of IoT devices, numerous challenges in terms of economical deployment and appropriate processing can be faced.
+... [another target-aligned mention] ...
+Data mining for IoT [26] Presents an overview of the features of data mining for IoT in line with future challenges and open issues.Ignores to present the IoT overview from various angles, such as semantics, devices, and Internet. WSN-based data centric IoT [3] Studies various functions of the economic and pricing prototypes, called intelligent log- ical decision-making techniques, to design procedures and systems for wireless sensor networks.Lakes to provide a partition of network trafﬁc into logical phases that affect the functionali- ties of WSNs. IoT-based cellular communications [1] Delivers a detailed explanation of the MTC development through various LTE releases and the newly designed MTC categories.Discusses only the physical layer features and neglects other important aspects, such as end- to-end network slicing and scalability issues for mobile IoT.
+... [another target-aligned mention] ...
+Real-Time analytics based IoT [29] Deﬁnes the essentials of the real-time IoT analytics and procedures, and clariﬁes limi- tations of the system policies for their valida- tion.Does not discuss protocols and applications that would assist the research community to choose appropriate technologies. with respect to WSN, WiFi, and cellular communications, iii) fog computing [19] with regard to users’ privacy and trust- worthiness, iv) data mining [26] in line with decentralized and heterogeneous techniques, v) data centric WSN [3] con- cerning mobility patterns and payment security, vi) cellular communications [1] with reference to obtaining frequency and operating cell IDs, vii) context-awareness [27] pertaining to device recognition and connection, viii) virtual objects [28] regarding their lifecycle and garbage collection, and ix) real-time analytics [29] in connection with scalability, fault tolerance, and massive data transmission. These challenges are addressed in the following subsections separately.
+... [another target-aligned mention] ...
+Pricing models for determining communica- tions and data gathering glitches in delivery networksLuonget al. [3] have provided economic models to determine communications and data aggregation issues in the IoT environment. Long Term Evolution (LTE-A)-based delivery networksElsaadany et al.
+... [another target-aligned mention] ...
+Hence, the server should keep track of the pattern of mobility of each in- dividual cellphone user [308]. In addition, payment security and bids’ conﬁdentiality [309] are two other prominent open research issues [3]. F.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.2400999999999999</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
       <c r="R35" s="3" t="inlineStr"/>
       <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3792,17 +3302,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>W2921968831-&gt;W2790400697</t>
+          <t>W4319769514-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Personal Data Trading Scheme for Data Brokers in IoT Data Marketplaces</t>
+          <t>Data-Driven Learning for Data Rights, Data Pricing, and Privacy Computing</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>Query-Based Data Pricing</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3812,71 +3322,54 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>[19]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>F. Liang, W. Yu, D. An, Q. Yang, X. Fu, and W. Zhao, “A Survey on Big Data Market: Pricing, Trading and Protection,” IEEE Access , vol. 6, pp. 15 132–15 154, 2018.</t>
+          <t>Koutris P, Upadhyaya P, Balazinska M, Howe B, Suciu D. Query-based data pricing. J ACM 2015;62(5):1–44 .</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>II. R ELATED WORK Data market and data trading issues have recently motivated studies to maximize revenues and proﬁts of data brokers (or data service providers) while satisfying data consumers (i.e., data buyers) [19]–[26]. Speciﬁcally, various data market structures for data trading like monopoly market, oligopoly market, and strong competition market were introduced in [19].
-... [another target-aligned mention] ...
-R ELATED WORK Data market and data trading issues have recently motivated studies to maximize revenues and proﬁts of data brokers (or data service providers) while satisfying data consumers (i.e., data buyers) [19]–[26]. Speciﬁcally, various data market structures for data trading like monopoly market, oligopoly market, and strong competition market were introduced in [19]. Niyato et al.</t>
+          <t>Koutris et al. [25] transformed the query-based pricing problem into a network ﬂow problem and automatically derived the price of any query from the price of a given set of views. After that, they adopted a dif- ferent perspective, which transformed the query-based pricing problem into optimized integer linear programming, priced the structured query language (SQL) query based on the price point speciﬁed by the seller, and used the query history to avoid the repeated charging of overlapping information [26].</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
       <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
-      <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3886,17 +3379,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>W2790400697-&gt;W2743929098</t>
+          <t>W4284704402-&gt;W3215634159</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>A Taxonomy on Smart Healthcare Technologies: Security Framework, Case Study, and Future Directions</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Data pricing strategy based on data quality</t>
+          <t>Coalition Game and Blockchain-Based Optimal Data Pricing Scheme for Ride Sharing Beyond 5G</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3906,69 +3399,54 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>[82]</t>
+          <t>[167]</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>H. Yu and M. Zhang, “Data pricing strategy based on data quality,” Computers &amp; Industrial Engineering, vol. 112, pp. 1–10, 2017.</t>
+          <t>R. Kakkar, R. Gupta, S. Tanwar, and J. J. P. C. Rodrigues, “Coalition game and blockchain-based optimal data pricing scheme for ride sharing beyond 5G,” IEEE Systems Journal , pp. 1–10, 2021.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
+          <t>[166]proposed a framework integrating blockchain and InterPlan- etary File System (IPFS) for sharing e-health data in a mobile cloud environment. They used smart contracts for secure e-health data [167]. But, data conﬁ dentiality is still not on point.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0.8999999999999999</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0.54675</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
       <c r="R37" s="3" t="inlineStr"/>
       <c r="S37" s="3" t="inlineStr"/>
-      <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="3" t="inlineStr"/>
-      <c r="V37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3978,17 +3456,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>W3202603574-&gt;W2974598553</t>
+          <t>W2327152018-&gt;W2010653253</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COVID-19 acceleration in digitalisation, aggregate productivity growth and the functional income distribution</t>
+          <t>AMUSE: Empowering Users for Cost-Aware Offloading with Throughput-Delay Tradeoffs</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Too Much Data: Prices and Inefficiencies in Data Markets</t>
+          <t>A survey of smart data pricing</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3998,22 +3476,22 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3386/ w23285 Acemoglu D, Makhdoumi A, Malekian A, Ozdaglar A (2019) Too much data: prices and inefficiencies in data markets. NBER Working Paper No. 26296. https:// doi. org/</t>
+          <t>S. Sen, C. Joe-Wong, S. Ha, and M. Chiang, “A survey of smart data pricing: Past proposals, current plans, and future trends,” ACM Computing Surveys , vol. 46, no. 2, p. 15, 2013.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>ICT manufacturing industries (operational) [B′ = 1 to 4] 261 [1] Manufacture of electronic components and boards 262 [2] Manufacture of computers and peripheral equipment 263 [3] Manufacture of communication equipment 264 [4] Manufacture of consumer electronics 582, 61, 62, 631, 951 C. ICT services industries (operational) [C = 8 + 9] 61 [8] T elecommunications 582, 62, 631, 951 [9] Computer and related activities [9 = 10 + 11 + 12 + 13] c) MC sector 581, 59, 60, 639 E. MC sector [E = F + G + H] 581 F.</t>
+          <t>To cope with this surge in data usage, which is driven by appli- cations such as mobile video, cloud services, and online magazines, many ISPs (Internet service providers) have adopted tiered pricing plans with monthly data caps to discourage heavy usage [2]. To further reduce network trafﬁc, many ISPs have also introduced supplementary networks such as WiFi hotspots or femtocells to ofﬂoad their cellular trafﬁc [3]–[5]. Such supplementary offer- ings introduce new challenges for users as they decide Y.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4023,44 +3501,29 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0.02025</t>
+          <t>0.0125</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
       <c r="R38" s="3" t="inlineStr"/>
       <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -4070,17 +3533,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>W4220901737-&gt;W2310916783</t>
+          <t>W4281710558-&gt;W3215634159</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Data Market Design: A Systematic Literature Review</t>
+          <t>Blockchain for Future Wireless Networks: A Decade Survey</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Marketplaces for Digital Data: Quo Vadis?</t>
+          <t>Coalition Game and Blockchain-Based Optimal Data Pricing Scheme for Ride Sharing Beyond 5G</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4090,77 +3553,54 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>[14]</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>F. Stahl, F. Schomm, L. Vomfell, and G. Vossen, ``Marketplaces for digital data: Quo vadis?'' Eur. Res. Center Inf. Syst., Münster, Germany, ERCIS Work. Paper 24, 2015.</t>
+          <t>Kakkar, R.; Gupta, R.; Tanwar, S.; Rodrigues, J.J.P .C. Coalition Game and Blockchain-Based Optimal Data Pricing Scheme for Ride Sharing Beyond 5G. IEEE Syst. J. 2021 , 1–10. . [CrossRef]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Finally, there exist some surveys such as the series of reports by Stahl et al. [14], and the work of Spiekermann [15]. These surveys look at real-world data markets in Europe, the U.S., and Israel to identify industry trends and reinforce the classi cation frameworks from the works above.
-... [another target-aligned mention] ...
-8) TIME FRAME The time frame dimension comes from the earlier classi ca- tion efforts of Schomm et al., and Stahl et al. [14], [24], [25]. This dimension concerns the currentness of the data, which can be either static, meaning it is factual data that is valu- able for an extended period (e.g., an image set that can be used for training a recurrent neural network) or dynamic, meaning it will quickly lose value over time (e.g., real-time traf c data).
-... [another target-aligned mention] ...
-and Stahl et al. [14], [24], [25]. They identi ed four potential values for this dimension: 1) API (application programming interface) pro- vides programmatic access to a data product via the internet, 2) download, meaning a data set is transferred from the data provider to the data consumer, 3) specialised software means that the data market uses a custom software solution to facilitate data transfer and 4) web interface means the data is presented to the data consumer on a website.
-... [another target-aligned mention] ...
-Based on these trial searches, we ended up with a relatively simple search string: ``data market'' OR ``data markets'' OR ``data marketplace'' OR ``data marketplaces.'' Selecting the right scholarly search engines is an impor- tant step in structured literature reviews [41], [53]. In this review, only academic search engines were because several works focusing on grey literature and data markets in industry already exist [14], [15], [21]. Since the goal of this structured literature review is to consider as many domains our possible, our selection of search engines should cover as a wide a scope as possible.
-... [another target-aligned mention] ...
-Afterwards, whenever possible, a comparison is made with the results from the previous surveys on data markets in industry by Stahl et al. (2015) [14], and Spiekermann (2019) [15]. One important thing to note is that the values in the dimensions are often not mutually exclusive; for example, a literature review can consider alltypes of matching models and, consequently, the sum of the percentages of each value in a dimension can exceed 100%.</t>
+          <t>The communication latency in 5G has decreased substantially, resulting in fast download and upload speeds. Although 5G networks are becoming a reality, technologists have already started to be engaged with fu- ture WNs, i.e., 6G, which anticipates putting greater prominence on wearable technologies, unmanned aerial vehicles (UAVs), 3D networking, and wireless power transfer to amplify people’s quality of life [ 31]. However, the radio resources used by the WNs operators are entirely open to security attacks, and therefore there is a need to explore and examine such attacks to stop them before they jeopardize the WN systems.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0.5346675000000001</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Result|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
       <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -4170,17 +3610,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2533772775</t>
+          <t>W2581979418-&gt;W1998665878</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>When Social Network Effect Meets Congestion Effect in Wireless Networks: Data Usage Equilibrium and Optimal Pricing</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>A pricing model for Big Personal Data</t>
+          <t>When Network Effect Meets Congestion Effect</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4190,71 +3630,58 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Yuncheng, S.; Bing, G.; Yan, S.; Xuliang, D.; Xiangqian, D.; Hong, Z. A pricing model for Big Personal Data. Tsinghua Sci. Technol. 2016 ,21, 482–490. [CrossRef]</t>
+          <t>X. Gong, L. Duan, and X. Chen, “When network effect meets congestion effect: Leveraging social services for wireless services,” in Proc. ACM MobiHoc 2015.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>[124] Market analysis Examining the market size and value of data marketplaces. [125–127] Pricing mechanismsDiscussing mathematical or economic approaches in evaluating, valuating, or pricing datasets (or data services) in data marketplaces.[47,128–145] Articles in the ﬁnance domain are not equally distributed across categories because most discussions are centralized in pricing mechanisms . Unlike the computational pricing in the STOF technology domain that focuses on technical aspects like query- or machine learning-based pricing (see Section 3.2), the pricing mechanisms here emphasize more on mathematical or economic approaches in valuating or pricing data in data marketplaces.
-... [another target-aligned mention] ...
-[ 131] propose pricing functions for aggregated personal data; Parra-Arnau [ 132] mathematically examine the tradeoff between privacy and money in personal data market; Yuncheng et al. [ 133] identify the properties that contribute to price personal data, such as data cost, value weight, information entropy, credit rating, and data reference index; Li et al. [ 134,135], discuss an economic theory of pricing personal data.</t>
+          <t xml:space="preserve">The corresponding author is Xu Chen. Part of this work was presented in ACM MobiHoc 2015 [1]. Social Domain 1 2 3 4 Network Effect Physical Domain 1 2 3 4 Congestion Effect Fig.
+... [another target-aligned mention] ...
+To our best knowledge, the interplay between network effect and congestion effect on users’ behavior in communication networks has not been explored. While part of this work has been presented in [1], more analytical results have been added in this paper. In particular, it is shown that when certain condition does not hold, there can exist multiple UDEs.
+... [another target-aligned mention] ...
+Content may change prior to final publication. Citation information: DOI 10.1109/JSAC.2017.2659059, IEEE Journal on Selected Areas in Communications Algorithm 2: Achieve the UDE in a distributed manner in Stage II 1each useri2N chooses an initial usage x(0) i0; 2loop at each time interval t= 1;2;::: 3each useri2N in parallel: 4updates its usage as x(t+1) i = arg max xi2[0;1)ui(xi;x(t) </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0.5900000000000001</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0.7200000000000001</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0.146202</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Discussion</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Discussion|mid|mid</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
       <c r="R40" s="3" t="inlineStr"/>
       <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="3" t="inlineStr"/>
-      <c r="V40" s="3" t="inlineStr"/>
     </row>
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -4264,17 +3691,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>W4210813858-&gt;W2910976764</t>
+          <t>W2734445852-&gt;W2293940046</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
+          <t>A First Look at Information Entropy-Based Data Pricing</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Nonrivalry and the Economics of Data</t>
+          <t>Query-Based Data Pricing</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4284,69 +3711,60 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[12]</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>C. I. Jones and C. Tonetti, ``Nonrivalry and the economics of data,'' Amer. Econ. Rev., vol. 110, no. 9, pp. 28192858, 2020.</t>
+          <t>P . Koutris, P . Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM (JACM) , vol. 62, no. 5, p. 43, 2015.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>A widely accepted approach for applications is to set prices to datasets directly based on their values. From an economic perspective, data value has been explored to study the impact on companies and industries [5][7]. From a computer science perspective, data value focuses on data compensation [8], [9] and data fusion [10], [11].</t>
+          <t>Nevertheless, data markets did not support complex ad-hoc queries at the beginning because it was unclear how to assign a proper price to a query result. Koutris et al proposed query-based data pricing framework to address complex ad-hoc queries [12]. Their framework allows data sellers to assign explicit prices to a few views or sets of views, and also provides the possibility to data buyers to issue and buy any query.
+... [another target-aligned mention] ...
+Their framework allows data sellers to assign explicit prices to a few views or sets of views, and also provides the possibility to data buyers to issue and buy any query. Although the price of queries can be calculated automatically from explicit prices of views using the framework proposed in [12], guidance for assigning reasonable price to views of datasets is not provided in [12]. 3) Bundling and Discrimination Pricing: Bundling pricing strategy originates from capital data market, and it represents anaggregation techniques [13].
+... [another target-aligned mention] ...
+As for information entropy-based pricing function presented in Section III-C, the biggest merit of proposed pricing function is the arbitrage-free property. Many of previous studies [16], [17], [12] concerning query-based data pricing dedicate to making the pricing function arbitrage-free. [16] proposed the rudiment of query-based data pricing, where a simple instance for calculation of query price for online data markets is provided.
+... [another target-aligned mention] ...
+Although subsequent researchers have proposed a variety of pricing functions based on [16], they still do not address the problem that the price for tuple (or view) is assigned subjectively by data owners. The proposed data pricing metric, data information entropy, might offer a new angle to address this problem in [16], [17], [12], because data information entropy could provide speciﬁc pricing relationship among tuples (views). IV .</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0.0379215</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Other|mid|low</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
       <c r="R41" s="3" t="inlineStr"/>
       <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="3" t="inlineStr"/>
-      <c r="V41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -4356,7 +3774,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>W3195579788-&gt;W2612128091</t>
+          <t>W3195579788-&gt;W3089176333</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4366,7 +3784,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>QIRANA</t>
+          <t>Towards Query Pricing on Incomplete Data</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4376,26 +3794,20 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Deep S, Koutris P (2017b) QIRANA: a framework for scalable query pricing. In: Salihoglu S, Zhou W, Chirkova R, Yang J, Suciu D (eds) Proceedings of the 2017 ACM international conference on 123 Data pricing in machine learning pipelines 1449 management of data, SIGMOD conference 2017, Chicago, IL, USA, May 14–19, 2017. ACM, pp 699–</t>
+          <t>Miao X, Gao Y , Chen L, Peng H, Yin J, Li Q (2020) Towards query pricing on incomplete data. IEEE Trans Knowl Data Eng</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>In a sell-side marketplace, the arbiter is operatedby a monopoly data seller to sell the single seller’s data products. In literature, sell-sidemarketplaces are considered by pricing models of both general data sets [ 43] and speciﬁc types of data products, such as XML documents [ 108] and data queries on a relational database [ 29]. A buy-side marketplace [ 120] ,a ss h o w ni nF i g .
-... [another target-aligned mention] ...
-Several examples of arbitrage-free pricing functionsare presented, including the weighted coverage function and the Shannon entropy function. Deep and Koutris [ 29] later implement the theoretical framework [ 28] into a real time pricing system, QIRANA, which computes the price of a query bundle Qfrom the view of uncertainty reduction. They assume that a buyer is facing a set of all possible databaseinstances Swith the same schema as the true database instance D.
+          <t>Miao et al. [ 75] study the problem of pricing selection-projection-natural join queries over incomplete databases. An arbitrage-free pricing function is proposed based on the idea ofdata provenance, which describes the origins of a piece of data and its processing history [ 10, 107].
 ... [another target-aligned mention] ...
 QueryMarket [ 59] tracks the purchased views of a customer and avoids charging those views when pricing future queries of the customer. Both[29]a n d[ 75] support history-aware pricing in the same vein as [ 59]. One drawback of these history-based approaches is that the seller must provide reliable storage to keep users’ queryhistory [ 111].
 ... [another target-aligned mention] ...
-By tracking coupon status, the data seller guarantees that each coupon will be usedonly once. However, the pricing function has no arbitrage-free guarantee [ 29]. 3.4 Privacy compensation Machine learning models in many areas, like recommendation systems [ 21] and personalized medical treatments [ 72], require a large amount of personal data.
-... [another target-aligned mention] ...
-Such ﬂexibility makes it easier to version raw data products, and enablesmore ﬂexible pricing mechanisms. For example, according to how much information isrevealed, different prices can be assigned to different queries on the same database [ 29]. 123 1442 Z.
-... [another target-aligned mention] ...
 Cong et al. Table 1 The representative data pricing models of raw data sets Product Objectives References General data No speciﬁc optimization goals [ 43] (1) Revenue maximization [ 117] Sensing data (1) Truthfulness; (2) Individual rationality; (3) Proﬁtability[115] (1) Truthfulness; (2) Social welfare maximization[52] (1) Truthfulness (2) Buyer’s cost minimization [ 60] Chain queries, conjunctive queries, and cyclic queries(1) Arbitrage-freeness; (2) Discount-freeness [ 58] Conjunctive queries (1) Arbitrage-freeness; (2) Discount-freeness; (3) History-awareness; (4) Fairness[59] General data queries (1) Arbitrage-freeness [ 28], [65] (1) Arbitrage-freeness; (2) History-awareness [ 29] (1) Arbitrage-freeness; (2) Revenue maximization[16] Selection-projection-natural join queries over incomplete databases(1) Arbitrage-freeness; (2) History-awareness [ 75] Selection queries (1) History-awareness [ 111] Counting queries on binary data (1) Privacy compensation; (2) Truthfulness; (3) Buyer’s cost minimization[38] Linear aggregation queries (1) Privacy compensation; (2) Query accuracy maximization under budget constraint[21] (1) Privacy compensation; (2) Personalized maximum tolerable privacy loss; (3) Queryaccuracy maximization under budgetconstraint[83] (1) Privacy compensation; (2) Truthfulness; (3) Personalized maximum tolerable privacy loss; (4) Query accuracy maximization under budget constraint[121] (1) Privacy compensation; (2) Arbitrage-freeness [ 62] (1) Privacy compensation; (2) Arbitrage-freeness; (3) Dependency fairness[84] Geo-location data (1) Privacy compensation; (2) Data accuracy maximization under budget constraint[53] tables can be used as a starting point in helping data pricing practitioners to choose the right pricing models for their settings. Tables 1,2,3,a n d 4have three columns.</t>
         </is>
       </c>
@@ -4406,49 +3818,34 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.4800000000000001</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="3" t="inlineStr"/>
       <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -4458,17 +3855,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>W2790400697-&gt;W2168402580</t>
+          <t>W3084177365-&gt;W2126626399</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
+          <t>A Survey on Data Pricing: From Economics to Data Science</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Query-based data pricing</t>
+          <t>The Price Is Right</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4478,69 +3875,54 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>[76]</t>
+          <t>[192]</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>P. Koutris, P. Upadhyaya, M. Balazinska, B. Howe, and D. Suciu, “Query-based data pricing,” Journal of the ACM (JACM), vol. 62, no. 5, p. 43, 2015.</t>
+          <t>R. Tang, H. Wu, Z. Bao, S. Bressan, and P . Valduriez, “The price is right,” in Database and Expert Systems Applications, H. Decker, L. Lhotsk ´a, S. Link, J. Basl, and A. M. Tjoa, Eds. Berlin, Heidelberg: Springer Berlin Heidelberg, 2013, pp. 380–394.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Market Structures Pricing Models Algorithms/Schemes Goals Approaches [16] Monopoly Economic-Based Pricing Information EntropyReduce uncertainty by reducing the information entropy to avoid the interference from uncertain data contentDeﬁne ﬁve tuples parameters for data and reduce the uncertainty information entropy [75] Strong competition Economic-Based Pricing Gaussian ProcessCapture the uncertain contents of source dataCreate a trading market, and simulate the trading process. Then, use statistics approach and Gaussian process to analyze the data trading and maximum proﬁt process [76] Monopoly Economic-Based Pricing Max-Flow problemImprove the transparency of data pricePropose a Generalized Chain Queries and obtain the price by computing the time complexity of GChQ query [77] Strong competitionGame Theory-Based PricingStackelberg Game-Based PricingUse pricing incentives method to improve the Quality of Service (QoS) and encourage upload data for the sensorsSet a bundle with data and service; use Stackelberg game to encourage the service and negotiate the data price with consumers [52] Monopoly Economic-Based PricingAlternate optimal multi-step pricing schemeCompute the most closest pricing in case of fallaciesPropose a general framework to compute the proﬁt for a licensed datasets pricing and consider with Willingness to Pay (WTP) of consumer side, and then obtain the maximizing proﬁt [78] Monopoly Economic-Based Pricing Economic-Based schemesCreate the differential digital productCalculate the differentiation of digital product and create the “differential delay”, then, pricing the digital product depends on the differentiations [79] MonopolyGame Theory-Based PricingStackelberg Game-Based PricingUse concave increasing function and Stackelberg game to maximize the proﬁt of datasetsCreate a digital market model with sensors, datasets, and consumers and use Stackelberg game model to obtain the maximum proﬁt [80] Strong competitionEconomic-Based Pricing and Auction-Based PricingEconomic-based schemes and Bargaining gameCalculate the cost and build economic modelBuild the economic model to analyze and calculate the cost of a certain datasets, and then, use Bargaining game to conﬁrm price of the datasets [81] Oligopoly Economic-Based PricingStatistics and Machine learning (Time-Dependent Pricing based on K-Nearest Neighbors (TDP-KNN) algorithm pricing algorithm and Time-Dependent Pricing based on Transition Rules (TDP-TR) pricing algorithm)Collect the usage of a certain datasetUse machine learning TDP-KNN algorithm) to collect and analyze the usage of some datasets and calculate the future usage expectation, and then, price the data [82] Monopoly Economic-Based Pricing Genetic algorithmDesign an assessment methods for exist data product and obtain its multi-dimensionality and dimensionsCreate a data-pricing tow level programming model depends on the quality and the proﬁt, and using genetic algorithm solves the model [83] Strong competition Economic-Based Pricing Snowballing AlgorithmDesign the market rule and the pricing modelsDesign a market model to create the selling database, and analyze the database 2169-3536 (c) 2018 IEEE. Translations and content mining are permitted for academic research only.</t>
+          <t>Tang et al. [192] follow the view and query based pricing framework and consider each tuple as the the minimum granularity of data. Their model assigns to each tuple a Authorized licensed use limited to: Carleton University.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0.8999999999999999</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0.54675</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
       <c r="R43" s="3" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -4550,17 +3932,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2734426755</t>
+          <t>W3195579788-&gt;W2126626399</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>Data pricing in machine learning pipelines</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>An Online Pricing Mechanism for Mobile Crowdsensing Data Markets</t>
+          <t>The Price Is Right</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4570,17 +3952,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Zheng, Z.; Peng, Y.; Wu, F.; Tang, S.; Chen, G. An online pricing mechanism for mobile crowdsensing data markets. In Proceedings of the 18th ACM International Symposium on Mobile Ad Hoc Networking and Computing, Chennai, India, 10–14 July 2017; pp. 1–10.</t>
+          <t>Tang R, Wu H, Bao Z, Bressan S, Valduriez P (2013) The price is right—models and algorithms for pricing data. In: Decker H, Lhotská L, Link S, Basl J, Tjoa AM (eds) Database and expert systems applications—24th international conference, DEXA 2013, Prague, Czech Republic, August 26–29, 2013. Proceedings, 123 Data pricing in machine learning pipelines 1453 part II, lecture notes in computer science, vol 8056. Springer, pp 380–394. https://doi.org/10.1007/978- 3-642-40173-2_31</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Another algorithm allows data price to be derived from the privacy losses [ 54]. Studies in query-based pricing mechanisms consider many cases such as query interfaces for mobile crowd-sensed data [ 55,56], cloud-based data mar- ketplaces with possibilities to share cloud resources [ 57], spatial data [ 58], aggregated data from multiple distributed system [ 59], and data acquired from Application Programming Interfaces (APIs) [ 60]. Moreover, Tang et al.</t>
+          <t>[ 75] study the problem of pricing selection-projection-natural join queries over incomplete databases. An arbitrage-free pricing function is proposed based on the idea ofdata provenance, which describes the origins of a piece of data and its processing history [ 10, 107]. Let tbe a tuple in a query answer Q(D).</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -4590,49 +3972,34 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0.3285599999999999</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>grouped|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
       <c r="R44" s="3" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr"/>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
     </row>
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -4642,45 +4009,37 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>W2921968831-&gt;W2759182208</t>
+          <t>W4226305897-&gt;W2916829860</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Personal Data Trading Scheme for Data Brokers in IoT Data Marketplaces</t>
+          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pricing privacy – the right to know the value of your personal data</t>
+          <t>ARETE: On Designing Joint Online Pricing and Reward Sharing Mechanisms for Mobile Data Markets</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>high_confidence</t>
+          <t>grouped</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>[18]</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>G. Malgieri and B. Custers, “Pricing privacy – the right to know the value of your personal data,” Computer Law &amp; Security Review, vol. 34, no. 2, pp. 289 – 303, 2018.</t>
+          <t>Zheng, Z.; Peng, Y.; Wu, F.; Tang, S.; Chen, G. ARETE: On Designing Joint Online Pricing and Reward Sharing Mechanisms for Mobile Data Markets. IEEE Trans. Mob. Comput. 2020 ,19, 769–787. [CrossRef]</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>The pro- posed WTB is also designed based on literature [17] to reﬂect real-world behaviors. This paper also proposes a personal data quality model for the collection of heterogeneous types of personal data by considering correlations of multiple personal data types as well as quantity of personal dataset based on literature [18] related to personal data pricing factors. The correlation of multiple personal data types is important to measure quality of personal dataset because when personal data is combined with other personal data, per- sonal data providers can potentially be identiﬁed through additional processing.
-... [another target-aligned mention] ...
-Content may change prior to final publication. Citation information: DOI 10.1109/ACCESS.2019.2904248, IEEE Access SUBMITTED TO IEEE ACCESS 3 and valuations of privacy (i.e., personal data pricing or pri- vacy pricing models) have also been studied [18], [28]–[33]. Malgieri and Custers investigated that the monetary value of personal data can be quantiﬁed with various personal data pricing factors [18].
-... [another target-aligned mention] ...
-Citation information: DOI 10.1109/ACCESS.2019.2904248, IEEE Access SUBMITTED TO IEEE ACCESS 3 and valuations of privacy (i.e., personal data pricing or pri- vacy pricing models) have also been studied [18], [28]–[33]. Malgieri and Custers investigated that the monetary value of personal data can be quantiﬁed with various personal data pricing factors [18]. Gkatzelis et al.
-... [another target-aligned mention] ...
-Quantifying the value and quality of personal data is an important factor to decide price of personal data. We choose several metrics to deﬁne the personal data quality function Q based on [18]. By analyzing various privacy regulations and researches, this work investigated privacy pricing factors as follows: sizeof dataset, completeness of dataset, a number of data types and their combinations, the level of identiﬁability of personal data.
-... [another target-aligned mention] ...
-There are many possible ways to increase the possibility for market participation of personal data providers; and in this paper, we have focused on a possible approach with personal data providers’ incentives. Since personal data now become a new ﬁnancial asset for individuals [10], this approach also has investigated in previous works [18], [28], [33]. However, it was still ambiguous about the feasibility of the IoT data market with personal data providers’ incentives; in other words, how 2169-3536 (c) 2018 IEEE.</t>
+          <t>Another algorithm allows data price to be derived from the privacy losses [ 54]. Studies in query-based pricing mechanisms consider many cases such as query interfaces for mobile crowd-sensed data [ 55,56], cloud-based data mar- ketplaces with possibilities to share cloud resources [ 57], spatial data [ 58], aggregated data from multiple distributed system [ 59], and data acquired from Application Programming Interfaces (APIs) [ 60]. Moreover, Tang et al.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -4690,49 +4049,34 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0.6091875</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -4742,17 +4086,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>W4210813858-&gt;W2612128091</t>
+          <t>W3089176333-&gt;W2126626399</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
+          <t>Towards Query Pricing on Incomplete Data</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>QIRANA</t>
+          <t>The Price Is Right</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4762,17 +4106,23 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>[27]</t>
+          <t>[26]</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>S. Deep and P. Koutris, ``QIRANA: A framework for scalable query pricing,'' in Proc. ACM Int. Conf. Manage. Data , May 2017, pp. 699713.</t>
+          <t>R. Tang, H. Wu, B. Zhifeng, K. Thomas, and B. Stephane, “The price is right, The price of relational and probabilistic relational data,” tech. rep., TRB5/12, 2012.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Researchers improved their studies and proposed a framework that allows the price of any query to be derived automatically [26]. QIRANA pricing sys- tem [27] allows exible pricing by allowing the data owners to choose from a variety of pricing functions, specify relation and attribute-level parameters to control the prices of queries. However, most queries considered by these marketplaces are too simplistic to support sophisticated data analytics and decision making.</t>
+          <t>5.1 Deriving the Lineage Sets We utilize two strategies, i.e., Active and Lazy, to seek lineage sets. They are the most appropriate methods for ﬁnding lineage tuples [26]. In particular, the main idea of Active is to track the procedure of performing the query Q, and record lineage sets simultaneously.
+... [another target-aligned mention] ...
+In addition, Baseline is able to get the price accurately, while it cannot be done by AD&amp;C. The approximate ratio AD&amp;C is equal to n, i.e., the number of result tuples stored in Q(D)[26]. The approximate ratio is the ratio of the approximate price (derived by AD&amp;C) to the exact price.
+... [another target-aligned mention] ...
+Furthermore, UCP is deﬁned as the multiplication of UP and the dataset complete rate (i.e., one minus the missing rate), which is more reasonable as it considers the data completeness. We generalize existing methods [26] to implement Active andLazy strategies, as they are the latest strategies to derive the query lineage set. Authorized licensed use limited to: University of Liverpool.
+... [another target-aligned mention] ...
+There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51]. In contrast, another kind of pricing scheme considers the tuples of relations as the structural granularity of the pricing function [15], [26], [52], [53]. It is usually based on the data lineage, i.e., the set of the tuples contributing to the result tuples of a query.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -4782,49 +4132,34 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="52" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -4834,17 +4169,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W4243417153</t>
+          <t>W3021370403-&gt;W2921968831</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Data Pricing: From Economics to Data Science</t>
+          <t>TIDES: A Trust-Aware IoT Data Economic System With Blockchain-Enabled Multi-Access Edge Computing</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Selling Cookies</t>
+          <t>Personal Data Trading Scheme for Data Brokers in IoT Data Marketplaces</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4854,17 +4189,23 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[18]</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>D. Bergemann and A. Bonatti, “Selling cookies,” American Eco- nomic Journal: Microeconomics, vol. 7, no. 3, pp. 259–94, August 2015.</t>
+          <t>H. Oh, S. Park, G. M. Lee, H. Heo, and J. K. Choi, ``Personal data trading scheme for data brokers in IoT data marketplaces,'' IEEE Access, vol. 7, pp. 4012040132, 2019.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>For example, the information about how customers are connected in social networks can be used to design customized discounts in marketing campaigns [215]. Bergemann and Bonatti [33] develop a model of pricing customer-level information such that the data about each customer are sold individually and individual queries to the database are priced linearly. As new technologies of customer tracking become available, more pricing models may emerge.</t>
+          <t>However, ignoring supplyconditions makes it dif cult to derive the most appro- priate price. Supply and demand model [17], [18]: In this kind of model, the relationship between suppliers and deman- ders is the most important factor for pricing. In [17], a linear supply function and a linear demand function are formulated to derive the price.
+... [another target-aligned mention] ...
+In [17], a linear supply function and a linear demand function are formulated to derive the price. In [18], a pricing system, called MGA, is proposed by formulating the willingness of suppliers and demanders as two natural logarithmic functions. Although the intersection of sup- plier and demander functions implies the price that has the best probability to reach a deal, the neglect of market situations, such as the competition between suppliers, leads to inappropriate pricing.
+... [another target-aligned mention] ...
+Note that QSDA dmust be greater than one because otherwise, DAwould be disquali ed for the demander. As concluded in [18] and [27], demanders intend to purchase the data commodity with higher C-P ratio. Thus, TIDES estimates the C-P ratio if dpurchases DAas follows, CPDA dD8 &gt;&lt; &gt;:vDA d PDAs;if PDA s&lt;PLDA d 0; otherwise(10) where PDA sis the price of DAset by s, and PLDA dis the acceptable price of DAset by d.
+... [another target-aligned mention] ...
+Since the intention that a demander purchases a commodity is related to its C-P ratio, the supplier should estimate the C-P ratio for its data commodity to be sold in the market by (12): CPDA estDPDA M PDAs(12) where pDA Mcan be obtained from the data trading KB. Then, based on [18], our pricing model proposes an exponential-based S function as in (13) for the supplier sto estimate the purchase intention of demanders to buy DA: PIDA sD0 @1Ce</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -4874,49 +4215,34 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.3674999999999999</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
       <c r="R47" s="3" t="inlineStr"/>
       <c r="S47" s="3" t="inlineStr"/>
-      <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="3" t="inlineStr"/>
-      <c r="V47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -4926,17 +4252,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>W3089176333-&gt;W2126626399</t>
+          <t>W2996741051-&gt;W2342966760</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Towards Query Pricing on Incomplete Data</t>
+          <t>Dynamic Pricing for Revenue Maximization in Mobile Social Data Market With Network Effects</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>The Price Is Right</t>
+          <t>Time and Location Aware Mobile Data Pricing</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4946,75 +4272,56 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>[26]</t>
+          <t>[33]</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R. Tang, H. Wu, B. Zhifeng, K. Thomas, and B. Stephane, “The price is right, The price of relational and probabilistic relational data,” tech. rep., TRB5/12, 2012.</t>
+          <t>Q. Ma, Y .-F. Liu and J. Huang, “Time and location aware mobile data pricing,” IEEE Transactions on Mobile Computing, vol. 15, no. 10, pp. 2599–2613, Ocotober 2016.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5.1 Deriving the Lineage Sets We utilize two strategies, i.e., Active and Lazy, to seek lineage sets. They are the most appropriate methods for ﬁnding lineage tuples [26]. In particular, the main idea of Active is to track the procedure of performing the query Q, and record lineage sets simultaneously.
-... [another target-aligned mention] ...
-In addition, Baseline is able to get the price accurately, while it cannot be done by AD&amp;C. The approximate ratio AD&amp;C is equal to n, i.e., the number of result tuples stored in Q(D)[26]. The approximate ratio is the ratio of the approximate price (derived by AD&amp;C) to the exact price.
-... [another target-aligned mention] ...
-Furthermore, UCP is deﬁned as the multiplication of UP and the dataset complete rate (i.e., one minus the missing rate), which is more reasonable as it considers the data completeness. We generalize existing methods [26] to implement Active andLazy strategies, as they are the latest strategies to derive the query lineage set. Authorized licensed use limited to: University of Liverpool.
-... [another target-aligned mention] ...
-There are some efforts on revenue maximizing arbitrage-free pricing [19], [43], [44], the pricing problem for trading time series data and personal data [45], [46], [47], [48], pricing queries while protecting the seller’s privacy [49], [50] or in cloud environments [51]. In contrast, another kind of pricing scheme considers the tuples of relations as the structural granularity of the pricing function [15], [26], [52], [53]. It is usually based on the data lineage, i.e., the set of the tuples contributing to the result tuples of a query.</t>
+          <t>Therefore, congestion effect from physical domain on user behaviors is also common [29]–[32]. For example, if an Internet network operator becomes oversubscribed, its sub- scribers suffer from the congestion due to limited bandwidth and radio resources [33]. Consequently, the model introduced in [8], [9], [27], [28] has a major limitation as it cannot be applied into the wireless network environments, in which the 1536-1276 (c) 2019 IEEE.
+... [another target-aligned mention] ...
+Citation information: DOI 10.1109/TWC.2019.2957092, IEEE Transactions on Wireless Communications 3 Table I COMPARISON OF OUR WORK WITH MOST RELATED WORKS ON PRICING Ref. Pricing goods Pricing scheme Network effects Congestion effects [29], [30], [32] Networking resources Static pricing  X [31] Networking resources Dynamic pricing  X [16], [33] Mobile data Dynamic pricing   [8], [9], [34] Social goods Static pricing X  [27], [28] Social goods Dynamic pricing X  [5] Mobile social data Static pricing X X Ours Mobile social data Dynamic pricing X X radio resource is scarce and congestion can frequently happen. As such, the question remains to be answered whether the network operators keep beneﬁting from network effects when congestion happens.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0.5346675000000001</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Result|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
       <c r="R48" s="3" t="inlineStr"/>
       <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="3" t="inlineStr"/>
-      <c r="V48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="52" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -5024,17 +4331,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>W4226305897-&gt;W2293940046</t>
+          <t>W2996741051-&gt;W2581979418</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Business Data Sharing through Data Marketplaces: A Systematic Literature Review</t>
+          <t>Dynamic Pricing for Revenue Maximization in Mobile Social Data Market With Network Effects</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Query-Based Data Pricing</t>
+          <t>When Social Network Effect Meets Congestion Effect in Wireless Networks: Data Usage Equilibrium and Optimal Pricing</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5044,69 +4351,70 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>[5]</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Koutris, P .; Upadhyaya, P .; Balazinska, M.; Howe, B.; Suciu, D. Query-Based Data Pricing. J. ACM 2015 ,62, 1–44. [CrossRef]</t>
+          <t>X. Gong, L. Duan, X. Chen and J. Zhang, “When social network effect meets congestion effect in wireless networks: Data usage equilibrium and optimal pricing,” IEEE Journal on Selected Areas in Communica- tions (JSAC), vol. 35, no. 2, pp. 449–462, February 2017.[6] J. Nie, J. Luo, Z. Xiong, D. Niyato and P. Wang, “A stackelberg game approach toward socially-aware incentive mechanisms for mobile crowdsensing,” IEEE Transactions on Wireless Communications, vol. 18, no. 1, pp. 724–738, 2019.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>This algorithm is applied in blockchain-based data marketplaces [50]. Next, publications in this category primarily propose query-based pricing mechanisms, referring to the capability to allow “the price of any query to be derived automatically” ([51], p. 43).</t>
+          <t>Therefore, as the mobile users pay the data fees to access the social services, the mobile network operator has an incentive to encourage more mobile users, i.e., its potential customers, to access the services by consuming more social data. Generally, the stronger the network effects are, the more revenue the mobile network operator gains [5], [6]. The “network effect” is often highlighted in social and economic ﬁelds [7].
+... [another target-aligned mention] ...
+The reason is that when users increase their data demand, they may bear higher congestion, e.g., service delay, which restrains them to access and consume more. Consequently, the increasing congestion creates a signiﬁcant barrier for the network operator, and thus leads to a lower revenue [5], [13]. Therefore, mobile users’ data demand is not only subject to the network effects in the social domain, but also the congestion effects in the network domain.
+... [another target-aligned mention] ...
+However, most of existing works ignore to take homophily phenomenon into consideration, i.e., network effects, for designing the data pricing. The social aspect of mobile networking is an emerging paradigm for network design and optimization [5]. In [25], the authors found that the information obtained from social tie connections will inﬂuence in decision making.
+... [another target-aligned mention] ...
+Citation information: DOI 10.1109/TWC.2019.2957092, IEEE Transactions on Wireless Communications 3 Table I COMPARISON OF OUR WORK WITH MOST RELATED WORKS ON PRICING Ref. Pricing goods Pricing scheme Network effects Congestion effects [29], [30], [32] Networking resources Static pricing  X [31] Networking resources Dynamic pricing  X [16], [33] Mobile data Dynamic pricing   [8], [9], [34] Social goods Static pricing X  [27], [28] Social goods Dynamic pricing X  [5] Mobile social data Static pricing X X Ours Mobile social data Dynamic pricing X X radio resource is scarce and congestion can frequently happen. As such, the question remains to be answered whether the network operators keep beneﬁting from network effects when congestion happens.
+... [another target-aligned mention] ...
+To fully exploit the beneﬁt of social data services, it is more appropriate to design the pricing considering both the network effects and congestion effects in a holistic manner, such that the network operators can adopt the best strategy towards its revenue maximization. To our best knowledge, only the work [5] proposed the data pricing schemes with the joint consideration of network effects and congestion effects. In [5], the authors formulated the interaction between a network operator and mobile users as a two-stage Stackelberg game, by extending the model presented in [8].
+... [another target-aligned mention] ...
+To our best knowledge, only the work [5] proposed the data pricing schemes with the joint consideration of network effects and congestion effects. In [5], the authors formulated the interaction between a network operator and mobile users as a two-stage Stackelberg game, by extending the model presented in [8]. In the upper Stage I of the formulated game, the service provider acting as the leader determines the price for users.
+... [another target-aligned mention] ...
+Then, the users acting as the followers simultaneously decide on the data demand maximizing their individual utilities given the price in the lower Stage II. Nevertheless, the authors in [5] merely formulated the one- shot game to model the interaction between the network operator and mobile users with static pricing. In other words, the operator cannot utilize its ability to modify its strategy in response to the observed history.
+... [another target-aligned mention] ...
+We assume that the MNO, i.e., the seller, has complete information about the social network and can perfectly charge each user differently, i.e., discriminatory pricing1[38]. The objective of the MNO is to maximize its revenue which is expressed as follows:  = max piX i2Npixi: (2) Naturally, the two-stage Stackelberg game can be adopted to model the interaction between the MNO and users [5], [13], [39]. In the upper Stage I, the MNO, i.e., the leader, determines price pito maximize its revenue.
+... [another target-aligned mention] ...
+Thus, if Assumption 1 does not hold, users may choose to un- boundedly increase their data demand for utility maximization irrespective of the pricing strategy. Therefore, following [5], [13], [41], we make the similar assumption to ensure that the social data demand from each user is bounded. Assumption 1 is dictated by the need for tractability and also essential for clearly illustrating our insights.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.243</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
       <c r="R49" s="3" t="inlineStr"/>
       <c r="S49" s="3" t="inlineStr"/>
-      <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -5116,17 +4424,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W2765365501</t>
+          <t>W4210813858-&gt;W2743929098</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Data Pricing: From Economics to Data Science</t>
+          <t>Data Boundary and Data Pricing Based on the Shapley Value</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Pricing of Data Products in Data Marketplaces</t>
+          <t>Data pricing strategy based on data quality</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5136,71 +4444,54 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>[75]</t>
+          <t>[18]</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>S. A. Fricker and Y. V . Maksimov, “Pricing of data products in data marketplaces,” in Software Business, A. Ojala, H. Holm-str¨om Olsson, and K. Werder, Eds. Cham: Springer International Publishing, 2017, pp. 49–66.</t>
+          <t>H. Yu and M. Zhang, ``Data pricing strategy based on data quality,'' Comput. Ind. Eng., vol. 112, pp. 110, Oct. 2017.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>They also discuss data trading and protection. Fricker and Maksimov [75] report a literature survey over 18 research articles regarding several research questions, including maturity of the pric- ing models. Very recently, Zhang and Beltr ´an [220] review the state-of-the-art data pricing methods.
-... [another target-aligned mention] ...
-Very recently, Zhang and Beltr ´an [220] review the state-of-the-art data pricing methods. They categorize data pricing methods according to two important data properties, granularity and privacy, This article covers a substantially broader scope than those [75], [136], [220]. We connect economics, digital product pricing and data product pricing.</t>
+          <t>Data-based pricing. They sell datasets and allow buyers to value the data directly based on the data features, including data information entropy levels [16], [17], data quality levels [18], [19], the fresh and real-time features [20], [21], and the amounts of data in the dataset [22]. Also, competitive data trading model [23] considered the willingness-to-sell of data providers and the willingness-to- pay of model buyers.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0.5109075000000001</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
       <c r="R50" s="3" t="inlineStr"/>
       <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="52" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -5210,17 +4501,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>W3084177365-&gt;W2743929098</t>
+          <t>W3021370403-&gt;W2790400697</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>A Survey on Data Pricing: From Economics to Data Science</t>
+          <t>TIDES: A Trust-Aware IoT Data Economic System With Blockchain-Enabled Multi-Access Edge Computing</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Data pricing strategy based on data quality</t>
+          <t>A Survey on Big Data Market: Pricing, Trading and Protection</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -5230,69 +4521,56 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>[219]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>H. Yu and M. Zhang, “Data pricing strategy based on data quality,” Computers &amp; Industrial Engineering, vol. 112, pp. 1 – 10, 2017.</t>
+          <t>F. Liang, W. Yu, D. An, Q. Yang, X. Fu, and W. Zhao, ``A survey on big data market: Pricing, trading and protection,'' IEEE Access, vol. 6, pp. 1513215154, 2018.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Another difﬁculty is that many data sets do not have public prices associated. Yu and Zhang [219] consider pricing multiple versions formed by multiple factors of data quality and build a two-level model. The ﬁrst level is the data platform where a single owner is assumed, who designs the number of versions.</t>
+          <t>Thus, IoT data trading is becoming active, and the establishment of trustworthy and reliable IoT data economic systems has become a necessity. Such systems must be able to ef ciently manage the life- cycle of IoT data, which typically consists of stages: data The associate editor coordinating the review of this manuscript and approving it for publication was Giovanni Merlino .collection, data analytics, data pricing, data trading, and data protection [1]. During data collection and data analytics, mas- sive amounts of heterogeneous data are collected and applied to generate useful knowledge, and the results are called data services.
+... [another target-aligned mention] ...
+C. DATA PRICING MODEL The data pricing models can be categorized into two types [1]. The economic-based pricing model evaluates the price of data according to economic principles, such as costs and margins.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0.4538699999999999</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>high_confidence|Methodology|high|high</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr"/>
       <c r="R51" s="3" t="inlineStr"/>
       <c r="S51" s="3" t="inlineStr"/>
-      <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="3" t="inlineStr"/>
-      <c r="V51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
